--- a/Översikt ROBERTSFORS.xlsx
+++ b/Översikt ROBERTSFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46097</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45701</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44919</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45250</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45944</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>45936</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>44473</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>45939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>45792</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>46070</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>46135</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>45796</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45967</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>45153</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>46050</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45891</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>45915</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>44725</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>45119</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>46037</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>45841</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>45848</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>44535</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>45560</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>45504</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>45051</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45177</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>45937</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>46038</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>46050</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>46050</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>46050</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>45182</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>46265</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>45182</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>45468</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>44699</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>44559</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>44803</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44497</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>45210</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5282,7 +5282,7 @@
         <v>45153</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>45233</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>45245</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>45856</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>45510</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>44823</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>45182</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>45146</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>45719</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>45124</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>45163</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>45630</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>45245</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         <v>46050</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>46050</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>46050</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>45957</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>46196</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>46198</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>45695</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         <v>46204</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>45712</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>45176</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>46269</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>45827</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>45835</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>45844</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>44312</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         <v>45747</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>45919</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>44784</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>44810</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         <v>44677</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>44880</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>44734</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>44734</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>44858</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         <v>44645</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>44572</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>44497</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         <v>44721</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
         <v>44612</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>44612</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>44658</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         <v>44641</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>44775</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>44575</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>44735</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>44795</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>44612</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         <v>44855</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>44473</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>44519</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>44571</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>44473</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>44844</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>44532</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>44482</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>44612</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
         <v>44612</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10747,7 +10747,7 @@
         <v>44851</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>44729</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>44819</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10971,7 +10971,7 @@
         <v>44662</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11044,7 +11044,7 @@
         <v>44697</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>44812</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11200,7 +11200,7 @@
         <v>44827</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>44841</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>44824</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>44475</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         <v>44580</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         <v>44574</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         <v>44641</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         <v>44644</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>44817</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>44615</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         <v>44488</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         <v>44789</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>44627</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>44627</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>45246</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>45687</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>45033</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>45625</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>45474</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>45537</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>45537</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>45048</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>45197</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>45548</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>45622</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>45700</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13128,7 +13128,7 @@
         <v>45253</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>45580</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13279,7 +13279,7 @@
         <v>45019</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>45079</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>45617</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>45496</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13576,7 +13576,7 @@
         <v>45484</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>45559</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>45559</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>45553</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>45405</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13946,7 +13946,7 @@
         <v>45572</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14019,7 +14019,7 @@
         <v>45184</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
         <v>44894</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>45659</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
         <v>45461</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14311,7 +14311,7 @@
         <v>45468</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14384,7 +14384,7 @@
         <v>44904</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14457,7 +14457,7 @@
         <v>45715</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>45446</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>44913</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>45070</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14749,7 +14749,7 @@
         <v>44902</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>44860</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>45251</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>45251</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>45197</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>45030</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>45695</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
         <v>45033</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>44805</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>45610</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>45687</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>44960</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>44960</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>45090</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>45202</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>44953</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>45149</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>45458</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         <v>45205</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16156,7 +16156,7 @@
         <v>45581</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16229,7 +16229,7 @@
         <v>45458</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>45715</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         <v>45617</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>45635</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>45029</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>44516</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>45191</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>45480</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16823,7 +16823,7 @@
         <v>45512</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>45281</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16969,7 +16969,7 @@
         <v>44783</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>45661</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>45664</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>44516</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>44838</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>45162</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         <v>45653</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17480,7 +17480,7 @@
         <v>44938</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>44945</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         <v>44487</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17704,7 +17704,7 @@
         <v>45544</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         <v>45826</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17855,7 +17855,7 @@
         <v>45701</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17928,7 +17928,7 @@
         <v>44901</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         <v>45930</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18074,7 +18074,7 @@
         <v>45889</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         <v>45890</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>45335</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18298,7 +18298,7 @@
         <v>45671</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18371,7 +18371,7 @@
         <v>45890</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>46139</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>45901</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>45895</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18673,7 +18673,7 @@
         <v>45893</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18746,7 +18746,7 @@
         <v>45929</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>45896</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>45405</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>45090</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>45734</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19121,7 +19121,7 @@
         <v>45903</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>45005</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
         <v>44580</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>45561</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19413,7 +19413,7 @@
         <v>46136</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>45246</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19564,7 +19564,7 @@
         <v>46141</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19642,7 +19642,7 @@
         <v>45541</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19720,7 +19720,7 @@
         <v>45909</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>46140</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19871,7 +19871,7 @@
         <v>45020</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19949,7 +19949,7 @@
         <v>45540</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>45915</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>44502</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45918</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20256,7 +20256,7 @@
         <v>45919</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20329,7 +20329,7 @@
         <v>45238</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20402,7 +20402,7 @@
         <v>45924</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20480,7 +20480,7 @@
         <v>45146</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20558,7 +20558,7 @@
         <v>45926</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20636,7 +20636,7 @@
         <v>45929</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>45251</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20792,7 +20792,7 @@
         <v>45510</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>45246</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>46146</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>45365</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>45162</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>46146</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
         <v>45938</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21313,7 +21313,7 @@
         <v>45357</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21386,7 +21386,7 @@
         <v>45712</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21459,7 +21459,7 @@
         <v>45628</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>46148</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21605,7 +21605,7 @@
         <v>45587</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21683,7 +21683,7 @@
         <v>45782</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         <v>45013</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>44973</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>46153</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>45042</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22053,7 +22053,7 @@
         <v>45679</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>44467</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         <v>45957</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>45141</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22350,7 +22350,7 @@
         <v>46150</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>45664</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>45957</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>46153</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22647,7 +22647,7 @@
         <v>45958</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22725,7 +22725,7 @@
         <v>46153</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>45959</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22876,7 +22876,7 @@
         <v>45959</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>46153</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23027,7 +23027,7 @@
         <v>45960</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>45961</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23183,7 +23183,7 @@
         <v>45965</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23256,7 +23256,7 @@
         <v>44936</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23329,7 +23329,7 @@
         <v>44734</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23402,7 +23402,7 @@
         <v>45965</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23475,7 +23475,7 @@
         <v>45965</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23548,7 +23548,7 @@
         <v>45966</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         <v>45205</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>45965</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         <v>45076</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>45020</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23923,7 +23923,7 @@
         <v>44475</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23996,7 +23996,7 @@
         <v>45974</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24074,7 +24074,7 @@
         <v>45981</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24152,7 +24152,7 @@
         <v>46155</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>45981</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24303,7 +24303,7 @@
         <v>45981</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24376,7 +24376,7 @@
         <v>44980</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>45002</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>45987</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24600,7 +24600,7 @@
         <v>45129</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24673,7 +24673,7 @@
         <v>45182</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24746,7 +24746,7 @@
         <v>45090</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24819,7 +24819,7 @@
         <v>45502</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>46160</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>46160</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         <v>45404</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>46160</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25189,7 +25189,7 @@
         <v>45610</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25267,7 +25267,7 @@
         <v>45302</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25340,7 +25340,7 @@
         <v>45611</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25413,7 +25413,7 @@
         <v>45475</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>45160</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>45996</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>45635</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25710,7 +25710,7 @@
         <v>45580</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25783,7 +25783,7 @@
         <v>45458</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>46000</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25929,7 +25929,7 @@
         <v>46000</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>45041</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>45133</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>45756</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>45678</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>45551</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>45268</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26455,7 +26455,7 @@
         <v>45307</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26528,7 +26528,7 @@
         <v>46169</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26606,7 +26606,7 @@
         <v>45607</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26679,7 +26679,7 @@
         <v>46171</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>46170</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>45470</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26898,7 +26898,7 @@
         <v>45301</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26971,7 +26971,7 @@
         <v>45712</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>45261</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27117,7 +27117,7 @@
         <v>45617</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>45160</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>45386</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>46037</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27409,7 +27409,7 @@
         <v>45176</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27482,7 +27482,7 @@
         <v>45365</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         <v>46171</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         <v>45548</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>46042</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27774,7 +27774,7 @@
         <v>45568</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>46042</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27920,7 +27920,7 @@
         <v>45667</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>45610</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28076,7 +28076,7 @@
         <v>44580</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>45526</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28227,7 +28227,7 @@
         <v>46048</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28300,7 +28300,7 @@
         <v>45432</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28373,7 +28373,7 @@
         <v>46050</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28446,7 +28446,7 @@
         <v>46175</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28519,7 +28519,7 @@
         <v>46050</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28592,7 +28592,7 @@
         <v>46050</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>46176</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28738,7 +28738,7 @@
         <v>45636</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28811,7 +28811,7 @@
         <v>45644</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28884,7 +28884,7 @@
         <v>46113</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28957,7 +28957,7 @@
         <v>45454</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29030,7 +29030,7 @@
         <v>45601</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29108,7 +29108,7 @@
         <v>46058</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>44876</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29259,7 +29259,7 @@
         <v>46059</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29332,7 +29332,7 @@
         <v>46059</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29405,7 +29405,7 @@
         <v>46063</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29478,7 +29478,7 @@
         <v>46177</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29551,7 +29551,7 @@
         <v>46065</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29624,7 +29624,7 @@
         <v>46065</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29697,7 +29697,7 @@
         <v>45463</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29770,7 +29770,7 @@
         <v>46181</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29843,7 +29843,7 @@
         <v>45029</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29916,7 +29916,7 @@
         <v>45678</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29994,7 +29994,7 @@
         <v>46076</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30067,7 +30067,7 @@
         <v>45565</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30140,7 +30140,7 @@
         <v>45627</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30213,7 +30213,7 @@
         <v>46183</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30286,7 +30286,7 @@
         <v>45215</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30359,7 +30359,7 @@
         <v>46083</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>46185</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>46185</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30578,7 +30578,7 @@
         <v>46188</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30651,7 +30651,7 @@
         <v>46185</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30724,7 +30724,7 @@
         <v>46188</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30797,7 +30797,7 @@
         <v>45049</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30870,7 +30870,7 @@
         <v>46188</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30943,7 +30943,7 @@
         <v>44901</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>45140</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31089,7 +31089,7 @@
         <v>46185</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>45600</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>46188</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>46094</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31391,7 +31391,7 @@
         <v>45250</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31464,7 +31464,7 @@
         <v>45610</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>45583</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31615,7 +31615,7 @@
         <v>46191</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31693,7 +31693,7 @@
         <v>46099</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31766,7 +31766,7 @@
         <v>45620</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31839,7 +31839,7 @@
         <v>44571</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31912,7 +31912,7 @@
         <v>44895</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31985,7 +31985,7 @@
         <v>46099</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32058,7 +32058,7 @@
         <v>46196</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32131,7 +32131,7 @@
         <v>46104</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>46198</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32277,7 +32277,7 @@
         <v>45468</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32350,7 +32350,7 @@
         <v>46105</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32423,7 +32423,7 @@
         <v>45545</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32496,7 +32496,7 @@
         <v>45664</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32569,7 +32569,7 @@
         <v>45708</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32642,7 +32642,7 @@
         <v>46112</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32715,7 +32715,7 @@
         <v>45496</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32793,7 +32793,7 @@
         <v>44622</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32871,7 +32871,7 @@
         <v>45082</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32944,7 +32944,7 @@
         <v>45644</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>44952</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33090,7 +33090,7 @@
         <v>44980</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33163,7 +33163,7 @@
         <v>46122</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>46122</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33309,7 +33309,7 @@
         <v>46126</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33382,7 +33382,7 @@
         <v>46126</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33455,7 +33455,7 @@
         <v>46244</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33528,7 +33528,7 @@
         <v>46126</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33601,7 +33601,7 @@
         <v>45708</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33674,7 +33674,7 @@
         <v>46202</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33747,7 +33747,7 @@
         <v>45184</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33825,7 +33825,7 @@
         <v>46204</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33903,7 +33903,7 @@
         <v>46133</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>46132</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>46132</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34132,7 +34132,7 @@
         <v>44952</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34205,7 +34205,7 @@
         <v>46132</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34283,7 +34283,7 @@
         <v>46135</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>46135</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34429,7 +34429,7 @@
         <v>46135</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34502,7 +34502,7 @@
         <v>45607</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34575,7 +34575,7 @@
         <v>46135</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34648,7 +34648,7 @@
         <v>45502</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34721,7 +34721,7 @@
         <v>45659</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>44980</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34867,7 +34867,7 @@
         <v>45182</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>46203</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>45631</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35086,7 +35086,7 @@
         <v>45145</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35164,7 +35164,7 @@
         <v>45135</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35242,7 +35242,7 @@
         <v>46206</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>46205</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>46205</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>45636</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35534,7 +35534,7 @@
         <v>45040</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>44683</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>45530</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35758,7 +35758,7 @@
         <v>44960</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35831,7 +35831,7 @@
         <v>44588</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35904,7 +35904,7 @@
         <v>46254</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35977,7 +35977,7 @@
         <v>46255</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36050,7 +36050,7 @@
         <v>46255</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>45659</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36196,7 +36196,7 @@
         <v>45525</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36269,7 +36269,7 @@
         <v>46259</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36342,7 +36342,7 @@
         <v>45692</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36415,7 +36415,7 @@
         <v>46258</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36488,7 +36488,7 @@
         <v>46258</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36561,7 +36561,7 @@
         <v>45671</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36634,7 +36634,7 @@
         <v>46261</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36712,7 +36712,7 @@
         <v>44551</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>46261</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36863,7 +36863,7 @@
         <v>44732</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36936,7 +36936,7 @@
         <v>44811</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37009,7 +37009,7 @@
         <v>44699</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37082,7 +37082,7 @@
         <v>44901</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37155,7 +37155,7 @@
         <v>45005</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37228,7 +37228,7 @@
         <v>45148</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>46195</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37379,7 +37379,7 @@
         <v>46262</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37457,7 +37457,7 @@
         <v>45670</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37530,7 +37530,7 @@
         <v>45687</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37603,7 +37603,7 @@
         <v>46266</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37676,7 +37676,7 @@
         <v>46225</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37749,7 +37749,7 @@
         <v>46225</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37822,7 +37822,7 @@
         <v>46225</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37895,7 +37895,7 @@
         <v>46266</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37968,7 +37968,7 @@
         <v>45701</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38041,7 +38041,7 @@
         <v>46269</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38119,7 +38119,7 @@
         <v>46268</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38192,7 +38192,7 @@
         <v>46269</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38270,7 +38270,7 @@
         <v>45161</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38343,7 +38343,7 @@
         <v>45246</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38416,7 +38416,7 @@
         <v>45246</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38489,7 +38489,7 @@
         <v>45160</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38562,7 +38562,7 @@
         <v>45644</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38635,7 +38635,7 @@
         <v>45628</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38708,7 +38708,7 @@
         <v>46269</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38786,7 +38786,7 @@
         <v>46273</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38859,7 +38859,7 @@
         <v>46268</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38937,7 +38937,7 @@
         <v>46230</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>46269</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>46269</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39166,7 +39166,7 @@
         <v>46273</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39239,7 +39239,7 @@
         <v>46279</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39312,7 +39312,7 @@
         <v>46279</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39390,7 +39390,7 @@
         <v>46276</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39463,7 +39463,7 @@
         <v>46279</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39541,7 +39541,7 @@
         <v>46279</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39619,7 +39619,7 @@
         <v>46276</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39697,7 +39697,7 @@
         <v>46280</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39775,7 +39775,7 @@
         <v>45495</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39853,7 +39853,7 @@
         <v>45642</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39926,7 +39926,7 @@
         <v>45188</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>46280</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>46239</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40150,7 +40150,7 @@
         <v>46239</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40223,7 +40223,7 @@
         <v>46240</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40301,7 +40301,7 @@
         <v>46240</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40374,7 +40374,7 @@
         <v>46240</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40447,7 +40447,7 @@
         <v>46240</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40520,7 +40520,7 @@
         <v>46239</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40593,7 +40593,7 @@
         <v>46282</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40671,7 +40671,7 @@
         <v>46239</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40744,7 +40744,7 @@
         <v>45794</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40817,7 +40817,7 @@
         <v>46240</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>45761</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40968,7 +40968,7 @@
         <v>46282</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41041,7 +41041,7 @@
         <v>46240</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41114,7 +41114,7 @@
         <v>46283</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41192,7 +41192,7 @@
         <v>46240</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>45800</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41338,7 +41338,7 @@
         <v>46240</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>45800</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41484,7 +41484,7 @@
         <v>45803</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41557,7 +41557,7 @@
         <v>45803</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41630,7 +41630,7 @@
         <v>45687</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41703,7 +41703,7 @@
         <v>45811</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41781,7 +41781,7 @@
         <v>45636</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41854,7 +41854,7 @@
         <v>45813</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>45818</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42000,7 +42000,7 @@
         <v>45831</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42073,7 +42073,7 @@
         <v>45832</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42151,7 +42151,7 @@
         <v>45839</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42224,7 +42224,7 @@
         <v>45474</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42302,7 +42302,7 @@
         <v>45839</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42375,7 +42375,7 @@
         <v>45839</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42448,7 +42448,7 @@
         <v>45839</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42521,7 +42521,7 @@
         <v>45839</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42594,7 +42594,7 @@
         <v>45839</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42667,7 +42667,7 @@
         <v>45841</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42740,7 +42740,7 @@
         <v>45841</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42813,7 +42813,7 @@
         <v>45856</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42886,7 +42886,7 @@
         <v>45856</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42959,7 +42959,7 @@
         <v>45856</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>45789</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43105,7 +43105,7 @@
         <v>45870</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43178,7 +43178,7 @@
         <v>45873</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43251,7 +43251,7 @@
         <v>44707</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43324,7 +43324,7 @@
         <v>44501</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43397,7 +43397,7 @@
         <v>45747</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43475,7 +43475,7 @@
         <v>45762</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43553,7 +43553,7 @@
         <v>46092</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>46147</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43699,7 +43699,7 @@
         <v>46149</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43772,7 +43772,7 @@
         <v>46155</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>

--- a/Översikt ROBERTSFORS.xlsx
+++ b/Översikt ROBERTSFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46097</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45701</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44919</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45250</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45936</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>45944</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>44473</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>45939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>45792</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>46070</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>46135</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>45796</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45967</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>46050</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>45153</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45891</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>45915</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>45848</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>45119</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>46037</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>44725</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>44535</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>46038</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>46050</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>46050</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>46050</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>45937</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>45051</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>45182</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>45468</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>45504</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>45177</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>45182</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>46265</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>45560</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>44699</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>44559</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>44803</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>44497</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>45210</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>46050</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>46050</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>46050</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>45146</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>45245</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>45182</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>45856</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>45163</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>45176</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         <v>45827</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>45719</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>45835</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>45124</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>45844</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>45957</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>45153</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>45630</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>45712</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         <v>46198</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>46204</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>45245</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>46269</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>45695</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>45510</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         <v>44823</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>45233</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>44312</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>45747</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>45919</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>44784</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8393,7 +8393,7 @@
         <v>44810</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>44677</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>44880</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>44734</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>44734</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>44858</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>44645</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>44572</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>44497</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>44721</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>44658</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>44612</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>44612</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>44641</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>44775</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>44575</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         <v>44795</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9644,7 +9644,7 @@
         <v>44735</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
         <v>44855</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>44612</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>44473</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         <v>44571</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>44519</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>44473</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
         <v>44532</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>44844</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>44482</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10384,7 +10384,7 @@
         <v>44612</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10457,7 +10457,7 @@
         <v>44612</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         <v>44851</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>44729</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>44819</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>44662</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>44697</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>44812</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>44827</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>44841</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>44824</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>44475</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>44580</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>44574</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>44641</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>44644</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>44817</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>44615</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>44488</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>44627</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>44627</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>44789</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>45715</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12088,7 +12088,7 @@
         <v>45268</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>45042</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>45029</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>45250</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>45253</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>44945</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>45526</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>45461</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>44902</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>44860</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
         <v>45551</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>45458</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>45544</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>44973</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>45794</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>45568</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>45496</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13344,7 +13344,7 @@
         <v>45761</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>45800</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>45889</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>45890</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13641,7 +13641,7 @@
         <v>45890</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>46037</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         <v>45893</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>46042</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         <v>45895</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>45631</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14084,7 +14084,7 @@
         <v>45896</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>44487</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14240,7 +14240,7 @@
         <v>46042</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         <v>44913</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>46048</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14459,7 +14459,7 @@
         <v>45162</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>44876</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>45800</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>46050</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14751,7 +14751,7 @@
         <v>45160</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14824,7 +14824,7 @@
         <v>46050</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14897,7 +14897,7 @@
         <v>46050</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14970,7 +14970,7 @@
         <v>45541</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>45540</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         <v>44894</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>45909</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15272,7 +15272,7 @@
         <v>44901</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
         <v>45357</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15418,7 +15418,7 @@
         <v>46058</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15496,7 +15496,7 @@
         <v>46059</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>45617</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>46059</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         <v>45915</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15793,7 +15793,7 @@
         <v>45918</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>46063</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15944,7 +15944,7 @@
         <v>45919</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>46065</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>45803</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16163,7 +16163,7 @@
         <v>46065</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>45924</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16314,7 +16314,7 @@
         <v>45803</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>45926</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>45678</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16543,7 +16543,7 @@
         <v>46076</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16616,7 +16616,7 @@
         <v>45030</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16689,7 +16689,7 @@
         <v>45636</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16762,7 +16762,7 @@
         <v>45929</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>45496</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>46083</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>45687</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>45404</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>45627</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>45938</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>45636</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>45679</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>45548</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>46094</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>46099</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>45782</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>46099</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>44732</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45600</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>46104</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>45184</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>46105</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>45246</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>45559</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>45712</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>45251</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>45559</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18544,7 +18544,7 @@
         <v>45607</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>46112</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18690,7 +18690,7 @@
         <v>45957</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
         <v>45958</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>45957</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18914,7 +18914,7 @@
         <v>45671</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>45959</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>45959</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19138,7 +19138,7 @@
         <v>44960</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19211,7 +19211,7 @@
         <v>44960</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19284,7 +19284,7 @@
         <v>44960</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19357,7 +19357,7 @@
         <v>46122</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19430,7 +19430,7 @@
         <v>45960</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>45961</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>45079</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>45965</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>45966</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19810,7 +19810,7 @@
         <v>45565</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>45020</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19961,7 +19961,7 @@
         <v>45965</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20034,7 +20034,7 @@
         <v>46122</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>44952</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20180,7 +20180,7 @@
         <v>46126</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>45965</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>45965</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>46126</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>44516</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>45090</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>45205</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>45813</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20764,7 +20764,7 @@
         <v>46126</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>45974</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>45818</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         <v>46132</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>45981</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21139,7 +21139,7 @@
         <v>45981</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21217,7 +21217,7 @@
         <v>45715</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21295,7 +21295,7 @@
         <v>45659</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>45981</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21446,7 +21446,7 @@
         <v>45667</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21524,7 +21524,7 @@
         <v>46135</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21597,7 +21597,7 @@
         <v>46135</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>46135</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>45987</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>45661</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21889,7 +21889,7 @@
         <v>45664</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21962,7 +21962,7 @@
         <v>45184</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22035,7 +22035,7 @@
         <v>45635</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         <v>45033</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22181,7 +22181,7 @@
         <v>46135</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22254,7 +22254,7 @@
         <v>45644</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22327,7 +22327,7 @@
         <v>45901</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>45734</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22478,7 +22478,7 @@
         <v>45458</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22551,7 +22551,7 @@
         <v>45996</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22624,7 +22624,7 @@
         <v>45205</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>46000</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22775,7 +22775,7 @@
         <v>45246</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22848,7 +22848,7 @@
         <v>46000</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>45692</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22994,7 +22994,7 @@
         <v>45182</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>45197</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>45701</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23218,7 +23218,7 @@
         <v>45502</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>46139</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>45561</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23437,7 +23437,7 @@
         <v>45238</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23510,7 +23510,7 @@
         <v>45040</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>45176</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>46140</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23734,7 +23734,7 @@
         <v>45145</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>45929</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
         <v>45687</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23963,7 +23963,7 @@
         <v>45005</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         <v>45826</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24109,7 +24109,7 @@
         <v>45636</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24182,7 +24182,7 @@
         <v>45146</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24260,7 +24260,7 @@
         <v>45930</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24333,7 +24333,7 @@
         <v>45002</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>45537</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>45133</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24562,7 +24562,7 @@
         <v>46146</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>46146</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>46148</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>45832</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
         <v>45831</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24937,7 +24937,7 @@
         <v>46150</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25015,7 +25015,7 @@
         <v>46153</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>45070</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
         <v>46153</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>46153</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>46153</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25390,7 +25390,7 @@
         <v>45090</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25463,7 +25463,7 @@
         <v>46155</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>44901</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25609,7 +25609,7 @@
         <v>44895</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>46160</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>45474</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25838,7 +25838,7 @@
         <v>46160</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25911,7 +25911,7 @@
         <v>45695</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25984,7 +25984,7 @@
         <v>46160</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>44980</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>45839</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26203,7 +26203,7 @@
         <v>45502</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         <v>45839</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>45839</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>45839</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>45839</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26568,7 +26568,7 @@
         <v>45839</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>45135</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         <v>45841</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>45617</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>45617</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26943,7 +26943,7 @@
         <v>45841</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27016,7 +27016,7 @@
         <v>44953</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27089,7 +27089,7 @@
         <v>44571</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>45587</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>45580</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>45856</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>45856</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27459,7 +27459,7 @@
         <v>45856</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>45405</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>45386</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>46171</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>45789</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>44901</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>46170</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27970,7 +27970,7 @@
         <v>46171</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28043,7 +28043,7 @@
         <v>45019</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28116,7 +28116,7 @@
         <v>45610</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28194,7 +28194,7 @@
         <v>46176</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28267,7 +28267,7 @@
         <v>45572</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28340,7 +28340,7 @@
         <v>46175</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28413,7 +28413,7 @@
         <v>45049</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28486,7 +28486,7 @@
         <v>45020</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28564,7 +28564,7 @@
         <v>45480</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28637,7 +28637,7 @@
         <v>46177</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         <v>45141</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>45281</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28861,7 +28861,7 @@
         <v>45468</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28934,7 +28934,7 @@
         <v>45475</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>45610</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29085,7 +29085,7 @@
         <v>45454</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         <v>45870</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29231,7 +29231,7 @@
         <v>46113</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29304,7 +29304,7 @@
         <v>45149</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29382,7 +29382,7 @@
         <v>45474</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29460,7 +29460,7 @@
         <v>45246</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29533,7 +29533,7 @@
         <v>45458</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29606,7 +29606,7 @@
         <v>46181</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29679,7 +29679,7 @@
         <v>46183</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29752,7 +29752,7 @@
         <v>44551</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29825,7 +29825,7 @@
         <v>45484</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29898,7 +29898,7 @@
         <v>46185</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29971,7 +29971,7 @@
         <v>46185</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30044,7 +30044,7 @@
         <v>46185</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30122,7 +30122,7 @@
         <v>45041</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30195,7 +30195,7 @@
         <v>45302</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30268,7 +30268,7 @@
         <v>45583</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30341,7 +30341,7 @@
         <v>46188</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30414,7 +30414,7 @@
         <v>45405</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30487,7 +30487,7 @@
         <v>46188</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>46188</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30633,7 +30633,7 @@
         <v>45873</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>45005</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>45620</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>45335</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30925,7 +30925,7 @@
         <v>45082</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>45712</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>45512</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>45678</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31222,7 +31222,7 @@
         <v>45182</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>45553</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31368,7 +31368,7 @@
         <v>45701</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>46198</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>45191</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31587,7 +31587,7 @@
         <v>46202</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>44580</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31733,7 +31733,7 @@
         <v>46203</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31806,7 +31806,7 @@
         <v>45610</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>44683</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31962,7 +31962,7 @@
         <v>46204</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32040,7 +32040,7 @@
         <v>46205</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>46205</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32186,7 +32186,7 @@
         <v>45625</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32259,7 +32259,7 @@
         <v>45601</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32337,7 +32337,7 @@
         <v>44805</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32410,7 +32410,7 @@
         <v>46206</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32483,7 +32483,7 @@
         <v>45687</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32556,7 +32556,7 @@
         <v>45708</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32629,7 +32629,7 @@
         <v>44588</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32702,7 +32702,7 @@
         <v>44622</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32780,7 +32780,7 @@
         <v>45653</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>45664</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32926,7 +32926,7 @@
         <v>46254</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32999,7 +32999,7 @@
         <v>44699</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33072,7 +33072,7 @@
         <v>45659</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33145,7 +33145,7 @@
         <v>46255</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>46255</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33291,7 +33291,7 @@
         <v>45611</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33364,7 +33364,7 @@
         <v>46258</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>46258</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>45670</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>44838</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33656,7 +33656,7 @@
         <v>45446</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33729,7 +33729,7 @@
         <v>45700</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33802,7 +33802,7 @@
         <v>46259</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33875,7 +33875,7 @@
         <v>45202</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33948,7 +33948,7 @@
         <v>46261</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34026,7 +34026,7 @@
         <v>46262</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34104,7 +34104,7 @@
         <v>46261</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>45708</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>46266</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>46266</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34401,7 +34401,7 @@
         <v>45756</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34474,7 +34474,7 @@
         <v>46195</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34547,7 +34547,7 @@
         <v>44783</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34620,7 +34620,7 @@
         <v>45463</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>46225</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34766,7 +34766,7 @@
         <v>46268</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>46225</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34912,7 +34912,7 @@
         <v>45301</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>46225</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35058,7 +35058,7 @@
         <v>46269</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>46269</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35214,7 +35214,7 @@
         <v>46269</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35292,7 +35292,7 @@
         <v>46268</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35370,7 +35370,7 @@
         <v>46269</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35448,7 +35448,7 @@
         <v>46269</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35526,7 +35526,7 @@
         <v>45013</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35599,7 +35599,7 @@
         <v>46273</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>46273</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35745,7 +35745,7 @@
         <v>46230</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35818,7 +35818,7 @@
         <v>46276</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35891,7 +35891,7 @@
         <v>46276</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>45537</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36047,7 +36047,7 @@
         <v>44938</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36120,7 +36120,7 @@
         <v>45261</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36193,7 +36193,7 @@
         <v>46279</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36266,7 +36266,7 @@
         <v>46279</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36344,7 +36344,7 @@
         <v>46280</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36422,7 +36422,7 @@
         <v>46280</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>45468</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36573,7 +36573,7 @@
         <v>46279</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36651,7 +36651,7 @@
         <v>46279</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36729,7 +36729,7 @@
         <v>45644</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36802,7 +36802,7 @@
         <v>46239</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>46239</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36948,7 +36948,7 @@
         <v>46282</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37021,7 +37021,7 @@
         <v>46240</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37094,7 +37094,7 @@
         <v>46282</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37172,7 +37172,7 @@
         <v>46239</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>46240</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
         <v>45510</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37396,7 +37396,7 @@
         <v>46240</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37469,7 +37469,7 @@
         <v>46240</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37542,7 +37542,7 @@
         <v>45622</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37615,7 +37615,7 @@
         <v>45671</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37688,7 +37688,7 @@
         <v>46239</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37761,7 +37761,7 @@
         <v>44980</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37839,7 +37839,7 @@
         <v>46283</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37917,7 +37917,7 @@
         <v>45581</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37990,7 +37990,7 @@
         <v>46240</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38063,7 +38063,7 @@
         <v>46185</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>46240</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38214,7 +38214,7 @@
         <v>46240</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38287,7 +38287,7 @@
         <v>46286</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38365,7 +38365,7 @@
         <v>45548</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>46286</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38516,7 +38516,7 @@
         <v>44516</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38589,7 +38589,7 @@
         <v>45033</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38662,7 +38662,7 @@
         <v>45048</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38735,7 +38735,7 @@
         <v>46288</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38808,7 +38808,7 @@
         <v>44936</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38881,7 +38881,7 @@
         <v>46244</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38954,7 +38954,7 @@
         <v>45432</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39027,7 +39027,7 @@
         <v>44811</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>46288</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39178,7 +39178,7 @@
         <v>46188</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39251,7 +39251,7 @@
         <v>46191</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>46196</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39402,7 +39402,7 @@
         <v>45607</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39475,7 +39475,7 @@
         <v>44502</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39548,7 +39548,7 @@
         <v>46289</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>44580</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>46240</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39777,7 +39777,7 @@
         <v>46289</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39850,7 +39850,7 @@
         <v>46132</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39928,7 +39928,7 @@
         <v>46289</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40006,7 +40006,7 @@
         <v>44467</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40079,7 +40079,7 @@
         <v>45580</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>45470</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40230,7 +40230,7 @@
         <v>45029</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>44734</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40376,7 +40376,7 @@
         <v>45076</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40449,7 +40449,7 @@
         <v>45129</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>45160</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40600,7 +40600,7 @@
         <v>44475</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40673,7 +40673,7 @@
         <v>45090</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40746,7 +40746,7 @@
         <v>44904</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40819,7 +40819,7 @@
         <v>45530</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40892,7 +40892,7 @@
         <v>45307</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40965,7 +40965,7 @@
         <v>45197</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41043,7 +41043,7 @@
         <v>45664</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41116,7 +41116,7 @@
         <v>45659</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41189,7 +41189,7 @@
         <v>45251</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41267,7 +41267,7 @@
         <v>45148</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41345,7 +41345,7 @@
         <v>45525</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41418,7 +41418,7 @@
         <v>45162</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>45365</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41564,7 +41564,7 @@
         <v>45365</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41637,7 +41637,7 @@
         <v>45610</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41715,7 +41715,7 @@
         <v>44980</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41788,7 +41788,7 @@
         <v>45215</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>45687</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>45545</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42007,7 +42007,7 @@
         <v>45635</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42080,7 +42080,7 @@
         <v>45628</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42153,7 +42153,7 @@
         <v>45251</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42226,7 +42226,7 @@
         <v>45644</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42299,7 +42299,7 @@
         <v>45628</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42372,7 +42372,7 @@
         <v>45160</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42445,7 +42445,7 @@
         <v>45161</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42518,7 +42518,7 @@
         <v>45246</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42591,7 +42591,7 @@
         <v>45246</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42664,7 +42664,7 @@
         <v>45642</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42737,7 +42737,7 @@
         <v>45495</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42815,7 +42815,7 @@
         <v>45188</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42888,7 +42888,7 @@
         <v>44707</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42961,7 +42961,7 @@
         <v>44501</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43034,7 +43034,7 @@
         <v>45747</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43112,7 +43112,7 @@
         <v>45762</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>46092</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43263,7 +43263,7 @@
         <v>46147</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43336,7 +43336,7 @@
         <v>46149</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43409,7 +43409,7 @@
         <v>46155</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>

--- a/Översikt ROBERTSFORS.xlsx
+++ b/Översikt ROBERTSFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46097</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45701</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44919</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45250</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45936</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>45944</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>44473</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>45939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>45792</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>46070</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>46135</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>45796</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45967</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>46050</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>45153</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45891</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>45915</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>45848</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>45119</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>46037</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>44725</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>44535</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>46038</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>46050</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>46050</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>46050</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>45937</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>45051</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>45182</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>45468</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>45504</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>45177</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>45182</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>46265</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>45560</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>44699</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>44559</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>44803</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>44497</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>45210</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>46050</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>46050</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>46050</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>45146</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>45245</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>45182</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>45856</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>45163</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>45176</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         <v>45827</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>45719</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>45835</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>45124</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>45844</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>45957</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>45153</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>45630</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>45712</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         <v>46198</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>46204</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>45245</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>46269</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>45695</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>45510</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         <v>44823</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>45233</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>44312</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>45747</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>45919</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>44784</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8393,7 +8393,7 @@
         <v>44810</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>44677</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>44880</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>44734</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>44734</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>44858</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>44645</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>44572</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>44497</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>44721</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>44658</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>44612</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>44612</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>44641</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>44775</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>44575</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         <v>44795</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9644,7 +9644,7 @@
         <v>44735</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
         <v>44855</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>44612</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>44473</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         <v>44571</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>44519</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>44473</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
         <v>44532</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>44844</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>44482</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10384,7 +10384,7 @@
         <v>44612</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10457,7 +10457,7 @@
         <v>44612</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         <v>44851</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>44729</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>44819</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>44662</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>44697</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>44812</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>44827</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>44841</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>44824</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>44475</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>44580</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>44574</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>44641</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>44644</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>44817</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>44615</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>44488</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>44627</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>44627</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>44789</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>45715</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12088,7 +12088,7 @@
         <v>45268</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>45042</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>45029</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>45250</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>45253</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>44945</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>45526</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>45461</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>44902</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>44860</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
         <v>45551</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>45458</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>45544</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>44973</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>45794</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>45568</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>45496</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13344,7 +13344,7 @@
         <v>45761</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>45800</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>45889</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>45890</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13641,7 +13641,7 @@
         <v>45890</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>46037</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         <v>45893</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>46042</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         <v>45895</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>45631</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14084,7 +14084,7 @@
         <v>45896</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>44487</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14240,7 +14240,7 @@
         <v>46042</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         <v>44913</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>46048</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14459,7 +14459,7 @@
         <v>45162</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>44876</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>45800</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>46050</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14751,7 +14751,7 @@
         <v>45160</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14824,7 +14824,7 @@
         <v>46050</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14897,7 +14897,7 @@
         <v>46050</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14970,7 +14970,7 @@
         <v>45541</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>45540</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         <v>44894</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>45909</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15272,7 +15272,7 @@
         <v>44901</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
         <v>45357</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15418,7 +15418,7 @@
         <v>46058</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15496,7 +15496,7 @@
         <v>46059</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>45617</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>46059</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         <v>45915</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15793,7 +15793,7 @@
         <v>45918</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>46063</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15944,7 +15944,7 @@
         <v>45919</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>46065</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>45803</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16163,7 +16163,7 @@
         <v>46065</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>45924</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16314,7 +16314,7 @@
         <v>45803</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>45926</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>45678</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16543,7 +16543,7 @@
         <v>46076</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16616,7 +16616,7 @@
         <v>45030</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16689,7 +16689,7 @@
         <v>45636</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16762,7 +16762,7 @@
         <v>45929</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>45496</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>46083</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>45687</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>45404</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>45627</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>45938</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>45636</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>45679</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>45548</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>46094</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>46099</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>45782</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>46099</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>44732</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45600</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>46104</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>45184</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>46105</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>45246</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>45559</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>45712</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>45251</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>45559</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18544,7 +18544,7 @@
         <v>45607</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>46112</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18690,7 +18690,7 @@
         <v>45957</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
         <v>45958</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>45957</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18914,7 +18914,7 @@
         <v>45671</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>45959</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>45959</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19138,7 +19138,7 @@
         <v>44960</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19211,7 +19211,7 @@
         <v>44960</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19284,7 +19284,7 @@
         <v>44960</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19357,7 +19357,7 @@
         <v>46122</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19430,7 +19430,7 @@
         <v>45960</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>45961</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>45079</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>45965</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>45966</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19810,7 +19810,7 @@
         <v>45565</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>45020</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19961,7 +19961,7 @@
         <v>45965</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20034,7 +20034,7 @@
         <v>46122</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>44952</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20180,7 +20180,7 @@
         <v>46126</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>45965</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>45965</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>46126</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>44516</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>45090</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>45205</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>45813</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20764,7 +20764,7 @@
         <v>46126</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>45974</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>45818</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         <v>46132</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>45981</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21139,7 +21139,7 @@
         <v>45981</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21217,7 +21217,7 @@
         <v>45715</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21295,7 +21295,7 @@
         <v>45659</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>45981</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21446,7 +21446,7 @@
         <v>45667</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21524,7 +21524,7 @@
         <v>46135</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21597,7 +21597,7 @@
         <v>46135</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>46135</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>45987</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>45661</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21889,7 +21889,7 @@
         <v>45664</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21962,7 +21962,7 @@
         <v>45184</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22035,7 +22035,7 @@
         <v>45635</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         <v>45033</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22181,7 +22181,7 @@
         <v>46135</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22254,7 +22254,7 @@
         <v>45644</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22327,7 +22327,7 @@
         <v>45901</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>45734</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22478,7 +22478,7 @@
         <v>45458</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22551,7 +22551,7 @@
         <v>45996</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22624,7 +22624,7 @@
         <v>45205</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>46000</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22775,7 +22775,7 @@
         <v>45246</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22848,7 +22848,7 @@
         <v>46000</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>45692</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22994,7 +22994,7 @@
         <v>45182</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>45197</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>45701</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23218,7 +23218,7 @@
         <v>45502</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>46139</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>45561</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23437,7 +23437,7 @@
         <v>45238</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23510,7 +23510,7 @@
         <v>45040</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>45176</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>46140</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23734,7 +23734,7 @@
         <v>45145</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>45929</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
         <v>45687</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23963,7 +23963,7 @@
         <v>45005</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         <v>45826</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24109,7 +24109,7 @@
         <v>45636</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24182,7 +24182,7 @@
         <v>45146</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24260,7 +24260,7 @@
         <v>45930</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24333,7 +24333,7 @@
         <v>45002</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>45537</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>45133</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24562,7 +24562,7 @@
         <v>46146</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>46146</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>46148</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>45832</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
         <v>45831</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24937,7 +24937,7 @@
         <v>46150</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25015,7 +25015,7 @@
         <v>46153</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>45070</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
         <v>46153</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>46153</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>46153</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25390,7 +25390,7 @@
         <v>45090</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25463,7 +25463,7 @@
         <v>46155</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>44901</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25609,7 +25609,7 @@
         <v>44895</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>46160</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>45474</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25838,7 +25838,7 @@
         <v>46160</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25911,7 +25911,7 @@
         <v>45695</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25984,7 +25984,7 @@
         <v>46160</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>44980</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>45839</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26203,7 +26203,7 @@
         <v>45502</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         <v>45839</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>45839</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>45839</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>45839</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26568,7 +26568,7 @@
         <v>45839</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>45135</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         <v>45841</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>45617</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>45617</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26943,7 +26943,7 @@
         <v>45841</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27016,7 +27016,7 @@
         <v>44953</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27089,7 +27089,7 @@
         <v>44571</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>45587</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>45580</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>45856</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>45856</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27459,7 +27459,7 @@
         <v>45856</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>45405</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>45386</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>46171</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>45789</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>44901</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>46170</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27970,7 +27970,7 @@
         <v>46171</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28043,7 +28043,7 @@
         <v>45019</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28116,7 +28116,7 @@
         <v>45610</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28194,7 +28194,7 @@
         <v>46176</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28267,7 +28267,7 @@
         <v>45572</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28340,7 +28340,7 @@
         <v>46175</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28413,7 +28413,7 @@
         <v>45049</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28486,7 +28486,7 @@
         <v>45020</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28564,7 +28564,7 @@
         <v>45480</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28637,7 +28637,7 @@
         <v>46177</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         <v>45141</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>45281</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28861,7 +28861,7 @@
         <v>45468</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28934,7 +28934,7 @@
         <v>45475</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>45610</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29085,7 +29085,7 @@
         <v>45454</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         <v>45870</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29231,7 +29231,7 @@
         <v>46113</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29304,7 +29304,7 @@
         <v>45149</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29382,7 +29382,7 @@
         <v>45474</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29460,7 +29460,7 @@
         <v>45246</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29533,7 +29533,7 @@
         <v>45458</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29606,7 +29606,7 @@
         <v>46181</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29679,7 +29679,7 @@
         <v>46183</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29752,7 +29752,7 @@
         <v>44551</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29825,7 +29825,7 @@
         <v>45484</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29898,7 +29898,7 @@
         <v>46185</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29971,7 +29971,7 @@
         <v>46185</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30044,7 +30044,7 @@
         <v>46185</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30122,7 +30122,7 @@
         <v>45041</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30195,7 +30195,7 @@
         <v>45302</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30268,7 +30268,7 @@
         <v>45583</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30341,7 +30341,7 @@
         <v>46188</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30414,7 +30414,7 @@
         <v>45405</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30487,7 +30487,7 @@
         <v>46188</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>46188</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30633,7 +30633,7 @@
         <v>45873</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>45005</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>45620</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>45335</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30925,7 +30925,7 @@
         <v>45082</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>45712</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>45512</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>45678</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31222,7 +31222,7 @@
         <v>45182</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>45553</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31368,7 +31368,7 @@
         <v>45701</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>46198</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>45191</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31587,7 +31587,7 @@
         <v>46202</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>44580</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31733,7 +31733,7 @@
         <v>46203</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31806,7 +31806,7 @@
         <v>45610</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>44683</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31962,7 +31962,7 @@
         <v>46204</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32040,7 +32040,7 @@
         <v>46205</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>46205</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32186,7 +32186,7 @@
         <v>45625</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32259,7 +32259,7 @@
         <v>45601</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32337,7 +32337,7 @@
         <v>44805</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32410,7 +32410,7 @@
         <v>46206</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32483,7 +32483,7 @@
         <v>45687</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32556,7 +32556,7 @@
         <v>45708</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32629,7 +32629,7 @@
         <v>44588</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32702,7 +32702,7 @@
         <v>44622</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32780,7 +32780,7 @@
         <v>45653</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>45664</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32926,7 +32926,7 @@
         <v>46254</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32999,7 +32999,7 @@
         <v>44699</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33072,7 +33072,7 @@
         <v>45659</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33145,7 +33145,7 @@
         <v>46255</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>46255</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33291,7 +33291,7 @@
         <v>45611</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33364,7 +33364,7 @@
         <v>46258</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>46258</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>45670</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>44838</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33656,7 +33656,7 @@
         <v>45446</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33729,7 +33729,7 @@
         <v>45700</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33802,7 +33802,7 @@
         <v>46259</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33875,7 +33875,7 @@
         <v>45202</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33948,7 +33948,7 @@
         <v>46261</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34026,7 +34026,7 @@
         <v>46262</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34104,7 +34104,7 @@
         <v>46261</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>45708</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>46266</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>46266</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34401,7 +34401,7 @@
         <v>45756</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34474,7 +34474,7 @@
         <v>46195</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34547,7 +34547,7 @@
         <v>44783</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34620,7 +34620,7 @@
         <v>45463</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>46225</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34766,7 +34766,7 @@
         <v>46268</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>46225</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34912,7 +34912,7 @@
         <v>45301</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>46225</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35058,7 +35058,7 @@
         <v>46269</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>46269</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35214,7 +35214,7 @@
         <v>46269</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35292,7 +35292,7 @@
         <v>46268</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35370,7 +35370,7 @@
         <v>46269</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35448,7 +35448,7 @@
         <v>46269</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35526,7 +35526,7 @@
         <v>45013</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35599,7 +35599,7 @@
         <v>46273</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>46273</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35745,7 +35745,7 @@
         <v>46230</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35818,7 +35818,7 @@
         <v>46276</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35891,7 +35891,7 @@
         <v>46276</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>45537</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36047,7 +36047,7 @@
         <v>44938</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36120,7 +36120,7 @@
         <v>45261</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36193,7 +36193,7 @@
         <v>46279</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36266,7 +36266,7 @@
         <v>46279</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36344,7 +36344,7 @@
         <v>46280</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36422,7 +36422,7 @@
         <v>46280</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>45468</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36573,7 +36573,7 @@
         <v>46279</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36651,7 +36651,7 @@
         <v>46279</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36729,7 +36729,7 @@
         <v>45644</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36802,7 +36802,7 @@
         <v>46239</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>46239</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36948,7 +36948,7 @@
         <v>46282</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37021,7 +37021,7 @@
         <v>46240</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37094,7 +37094,7 @@
         <v>46282</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37172,7 +37172,7 @@
         <v>46239</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>46240</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
         <v>45510</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37396,7 +37396,7 @@
         <v>46240</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37469,7 +37469,7 @@
         <v>46240</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37542,7 +37542,7 @@
         <v>45622</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37615,7 +37615,7 @@
         <v>45671</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37688,7 +37688,7 @@
         <v>46239</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37761,7 +37761,7 @@
         <v>44980</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37839,7 +37839,7 @@
         <v>46283</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37917,7 +37917,7 @@
         <v>45581</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37990,7 +37990,7 @@
         <v>46240</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38063,7 +38063,7 @@
         <v>46185</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>46240</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38214,7 +38214,7 @@
         <v>46240</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38287,7 +38287,7 @@
         <v>46286</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38365,7 +38365,7 @@
         <v>45548</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>46286</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38516,7 +38516,7 @@
         <v>44516</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38589,7 +38589,7 @@
         <v>45033</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38662,7 +38662,7 @@
         <v>45048</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38735,7 +38735,7 @@
         <v>46288</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38808,7 +38808,7 @@
         <v>44936</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38881,7 +38881,7 @@
         <v>46244</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38954,7 +38954,7 @@
         <v>45432</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39027,7 +39027,7 @@
         <v>44811</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>46288</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39178,7 +39178,7 @@
         <v>46188</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39251,7 +39251,7 @@
         <v>46191</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>46196</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39402,7 +39402,7 @@
         <v>45607</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39475,7 +39475,7 @@
         <v>44502</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39548,7 +39548,7 @@
         <v>46289</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>44580</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>46240</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39777,7 +39777,7 @@
         <v>46289</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39850,7 +39850,7 @@
         <v>46132</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39928,7 +39928,7 @@
         <v>46289</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40006,7 +40006,7 @@
         <v>44467</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40079,7 +40079,7 @@
         <v>45580</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>45470</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40230,7 +40230,7 @@
         <v>45029</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>44734</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40376,7 +40376,7 @@
         <v>45076</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40449,7 +40449,7 @@
         <v>45129</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>45160</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40600,7 +40600,7 @@
         <v>44475</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40673,7 +40673,7 @@
         <v>45090</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40746,7 +40746,7 @@
         <v>44904</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40819,7 +40819,7 @@
         <v>45530</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40892,7 +40892,7 @@
         <v>45307</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40965,7 +40965,7 @@
         <v>45197</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41043,7 +41043,7 @@
         <v>45664</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41116,7 +41116,7 @@
         <v>45659</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41189,7 +41189,7 @@
         <v>45251</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41267,7 +41267,7 @@
         <v>45148</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41345,7 +41345,7 @@
         <v>45525</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41418,7 +41418,7 @@
         <v>45162</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>45365</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41564,7 +41564,7 @@
         <v>45365</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41637,7 +41637,7 @@
         <v>45610</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41715,7 +41715,7 @@
         <v>44980</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41788,7 +41788,7 @@
         <v>45215</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>45687</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>45545</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42007,7 +42007,7 @@
         <v>45635</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42080,7 +42080,7 @@
         <v>45628</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42153,7 +42153,7 @@
         <v>45251</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42226,7 +42226,7 @@
         <v>45644</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42299,7 +42299,7 @@
         <v>45628</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42372,7 +42372,7 @@
         <v>45160</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42445,7 +42445,7 @@
         <v>45161</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42518,7 +42518,7 @@
         <v>45246</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42591,7 +42591,7 @@
         <v>45246</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42664,7 +42664,7 @@
         <v>45642</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42737,7 +42737,7 @@
         <v>45495</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42815,7 +42815,7 @@
         <v>45188</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42888,7 +42888,7 @@
         <v>44707</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42961,7 +42961,7 @@
         <v>44501</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43034,7 +43034,7 @@
         <v>45747</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43112,7 +43112,7 @@
         <v>45762</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>46092</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43263,7 +43263,7 @@
         <v>46147</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43336,7 +43336,7 @@
         <v>46149</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43409,7 +43409,7 @@
         <v>46155</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>

--- a/Översikt ROBERTSFORS.xlsx
+++ b/Översikt ROBERTSFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46097</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45701</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44919</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45250</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45944</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>45936</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>44473</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>45939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>45792</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>46070</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>46135</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>45796</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45967</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>45153</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>46050</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45891</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>45915</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>45848</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>44725</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>45119</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>46037</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>44535</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>45560</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>45504</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>45051</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>46038</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>46050</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>46050</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>46050</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>45937</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>45177</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>45468</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>46265</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>45182</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>45182</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>44699</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>44559</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>44803</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>44497</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>45210</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>46050</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>46050</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>46050</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>45153</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>45233</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>45245</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>45827</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>45835</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>45510</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>44823</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>45844</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>45856</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>45146</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>45182</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>45124</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>45719</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>45957</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>45163</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         <v>45630</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>46198</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>46204</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>45245</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>46269</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>45695</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>45712</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>45176</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>44312</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>45747</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>45919</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>44784</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8393,7 +8393,7 @@
         <v>44810</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>44677</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>44880</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>44734</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>44734</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>44858</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>44645</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>44572</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>44497</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>44721</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>44658</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>44612</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>44612</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>44641</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>44775</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>44575</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         <v>44735</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9644,7 +9644,7 @@
         <v>44795</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
         <v>44855</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>44612</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>44473</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         <v>44519</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>44571</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>44473</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
         <v>44532</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>44844</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>44482</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10384,7 +10384,7 @@
         <v>44612</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10457,7 +10457,7 @@
         <v>44612</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         <v>44851</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>44729</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>44819</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>44662</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>44697</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>44812</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>44827</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>44841</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>44824</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>44475</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>44580</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>44574</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>44641</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>44644</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>44817</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>44615</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>44488</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>44627</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>44627</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>44789</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>45687</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12088,7 +12088,7 @@
         <v>45246</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>45625</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>45079</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>45033</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>45474</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>45537</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>45537</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>45048</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>45548</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>45197</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>45700</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         <v>45580</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12989,7 +12989,7 @@
         <v>45622</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>45617</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13135,7 +13135,7 @@
         <v>45253</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>45405</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
         <v>45019</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>45184</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>45495</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>45642</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>45496</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>45553</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         <v>45484</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13802,7 +13802,7 @@
         <v>45572</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         <v>45188</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13948,7 +13948,7 @@
         <v>45559</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>45559</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>45889</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>45890</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>44894</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>45890</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>45895</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>45893</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>45896</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>45659</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>45461</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         <v>46037</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>45541</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14922,7 +14922,7 @@
         <v>45468</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>45909</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15068,7 +15068,7 @@
         <v>46042</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15141,7 +15141,7 @@
         <v>45540</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>44904</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>46042</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>45715</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15438,7 +15438,7 @@
         <v>45915</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15516,7 +15516,7 @@
         <v>45794</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>45761</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>46048</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15735,7 +15735,7 @@
         <v>45446</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>45800</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>46050</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>45918</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>45800</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
         <v>45919</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>45803</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
         <v>44960</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16324,7 +16324,7 @@
         <v>44960</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16397,7 +16397,7 @@
         <v>46050</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>45803</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16543,7 +16543,7 @@
         <v>46050</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16616,7 +16616,7 @@
         <v>45924</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>44913</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45070</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>46058</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>45926</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>45929</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>46059</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>46059</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>45251</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>46063</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>46065</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>44902</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>45197</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17590,7 +17590,7 @@
         <v>46065</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17663,7 +17663,7 @@
         <v>45030</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17736,7 +17736,7 @@
         <v>44860</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17809,7 +17809,7 @@
         <v>45687</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>45251</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>45938</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>45695</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>45033</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18179,7 +18179,7 @@
         <v>45678</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18257,7 +18257,7 @@
         <v>44805</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>45610</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>45636</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>45687</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18554,7 +18554,7 @@
         <v>46076</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>45782</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>45090</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>45202</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18846,7 +18846,7 @@
         <v>44953</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>46083</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18992,7 +18992,7 @@
         <v>45957</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>45149</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>45813</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>45957</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19289,7 +19289,7 @@
         <v>45958</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>45959</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>45458</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>45959</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>45960</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19669,7 +19669,7 @@
         <v>45961</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>45205</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19820,7 +19820,7 @@
         <v>45965</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>45965</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>45581</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20039,7 +20039,7 @@
         <v>45965</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>46094</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20190,7 +20190,7 @@
         <v>45617</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>45966</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20346,7 +20346,7 @@
         <v>45965</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20419,7 +20419,7 @@
         <v>45715</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20497,7 +20497,7 @@
         <v>45458</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20570,7 +20570,7 @@
         <v>45635</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20643,7 +20643,7 @@
         <v>46099</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20716,7 +20716,7 @@
         <v>46099</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20789,7 +20789,7 @@
         <v>46104</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>45974</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20940,7 +20940,7 @@
         <v>45029</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21013,7 +21013,7 @@
         <v>46105</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21086,7 +21086,7 @@
         <v>45818</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21159,7 +21159,7 @@
         <v>45981</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21237,7 +21237,7 @@
         <v>44516</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21310,7 +21310,7 @@
         <v>45981</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21388,7 +21388,7 @@
         <v>45981</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>45480</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         <v>45661</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>45664</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
         <v>44516</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21753,7 +21753,7 @@
         <v>46112</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21826,7 +21826,7 @@
         <v>45281</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21899,7 +21899,7 @@
         <v>45987</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21972,7 +21972,7 @@
         <v>45191</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>45512</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22118,7 +22118,7 @@
         <v>44783</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22191,7 +22191,7 @@
         <v>44838</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>45162</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22337,7 +22337,7 @@
         <v>45653</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22410,7 +22410,7 @@
         <v>44938</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>46122</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22556,7 +22556,7 @@
         <v>46122</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22629,7 +22629,7 @@
         <v>44945</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22702,7 +22702,7 @@
         <v>44487</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22780,7 +22780,7 @@
         <v>46126</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22853,7 +22853,7 @@
         <v>46126</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22926,7 +22926,7 @@
         <v>46126</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22999,7 +22999,7 @@
         <v>45996</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23072,7 +23072,7 @@
         <v>45544</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23150,7 +23150,7 @@
         <v>45831</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>45701</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>46000</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23369,7 +23369,7 @@
         <v>46000</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23447,7 +23447,7 @@
         <v>44901</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23520,7 +23520,7 @@
         <v>46132</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>45832</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23676,7 +23676,7 @@
         <v>46135</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23749,7 +23749,7 @@
         <v>46135</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23822,7 +23822,7 @@
         <v>45335</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23895,7 +23895,7 @@
         <v>45671</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23968,7 +23968,7 @@
         <v>46135</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>46135</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24114,7 +24114,7 @@
         <v>45502</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24187,7 +24187,7 @@
         <v>45839</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24260,7 +24260,7 @@
         <v>45474</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24338,7 +24338,7 @@
         <v>45839</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>45839</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>45839</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24557,7 +24557,7 @@
         <v>45839</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>45145</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>45839</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24781,7 +24781,7 @@
         <v>45405</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24854,7 +24854,7 @@
         <v>45090</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24927,7 +24927,7 @@
         <v>45841</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         <v>45841</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>45005</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25146,7 +25146,7 @@
         <v>44580</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25219,7 +25219,7 @@
         <v>45020</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25297,7 +25297,7 @@
         <v>45826</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25370,7 +25370,7 @@
         <v>44502</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25443,7 +25443,7 @@
         <v>45930</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25516,7 +25516,7 @@
         <v>46139</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25589,7 +25589,7 @@
         <v>45901</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25667,7 +25667,7 @@
         <v>45929</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25745,7 +25745,7 @@
         <v>45734</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>45856</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>45856</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25964,7 +25964,7 @@
         <v>45856</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26037,7 +26037,7 @@
         <v>45789</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>45561</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26183,7 +26183,7 @@
         <v>45246</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26256,7 +26256,7 @@
         <v>46140</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26334,7 +26334,7 @@
         <v>45251</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26412,7 +26412,7 @@
         <v>45510</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>45246</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26563,7 +26563,7 @@
         <v>45365</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>45162</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>45357</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26782,7 +26782,7 @@
         <v>45712</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         <v>45628</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>45587</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         <v>45238</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>45146</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>45870</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>45013</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>44973</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>46146</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27454,7 +27454,7 @@
         <v>45042</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27527,7 +27527,7 @@
         <v>45679</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27600,7 +27600,7 @@
         <v>46146</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27673,7 +27673,7 @@
         <v>46148</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27746,7 +27746,7 @@
         <v>45141</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>45664</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>46153</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>46150</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>46153</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>46153</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>46153</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>44936</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>44734</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>46155</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>45205</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28569,7 +28569,7 @@
         <v>45076</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28642,7 +28642,7 @@
         <v>45502</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28715,7 +28715,7 @@
         <v>45020</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28793,7 +28793,7 @@
         <v>46160</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28866,7 +28866,7 @@
         <v>44475</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>46160</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>45873</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29085,7 +29085,7 @@
         <v>46160</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29163,7 +29163,7 @@
         <v>45580</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29236,7 +29236,7 @@
         <v>44980</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29314,7 +29314,7 @@
         <v>45002</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29387,7 +29387,7 @@
         <v>46171</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29460,7 +29460,7 @@
         <v>46170</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29533,7 +29533,7 @@
         <v>45129</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29606,7 +29606,7 @@
         <v>45182</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29679,7 +29679,7 @@
         <v>45386</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29752,7 +29752,7 @@
         <v>45090</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29825,7 +29825,7 @@
         <v>46171</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29898,7 +29898,7 @@
         <v>46175</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29971,7 +29971,7 @@
         <v>46176</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30044,7 +30044,7 @@
         <v>46113</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30117,7 +30117,7 @@
         <v>45454</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30190,7 +30190,7 @@
         <v>45404</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30263,7 +30263,7 @@
         <v>45610</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30341,7 +30341,7 @@
         <v>45302</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30414,7 +30414,7 @@
         <v>46177</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30487,7 +30487,7 @@
         <v>45611</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>46181</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30633,7 +30633,7 @@
         <v>45475</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>45160</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30784,7 +30784,7 @@
         <v>45635</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>46183</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>46185</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31003,7 +31003,7 @@
         <v>46185</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31076,7 +31076,7 @@
         <v>45458</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>46188</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31222,7 +31222,7 @@
         <v>46188</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>46188</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31368,7 +31368,7 @@
         <v>46185</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>45041</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31519,7 +31519,7 @@
         <v>45133</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31597,7 +31597,7 @@
         <v>45756</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31670,7 +31670,7 @@
         <v>45620</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31743,7 +31743,7 @@
         <v>45678</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31821,7 +31821,7 @@
         <v>45551</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31894,7 +31894,7 @@
         <v>46198</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31967,7 +31967,7 @@
         <v>45268</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32040,7 +32040,7 @@
         <v>45307</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>45607</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32186,7 +32186,7 @@
         <v>45470</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32259,7 +32259,7 @@
         <v>45301</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32332,7 +32332,7 @@
         <v>45712</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32405,7 +32405,7 @@
         <v>46202</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32478,7 +32478,7 @@
         <v>46204</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32556,7 +32556,7 @@
         <v>45261</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32629,7 +32629,7 @@
         <v>46203</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32702,7 +32702,7 @@
         <v>45617</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         <v>45160</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32848,7 +32848,7 @@
         <v>46206</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32921,7 +32921,7 @@
         <v>46205</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32994,7 +32994,7 @@
         <v>46205</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33067,7 +33067,7 @@
         <v>45176</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33140,7 +33140,7 @@
         <v>45365</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33213,7 +33213,7 @@
         <v>45548</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33286,7 +33286,7 @@
         <v>45568</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33359,7 +33359,7 @@
         <v>45667</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>45610</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33515,7 +33515,7 @@
         <v>44580</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33588,7 +33588,7 @@
         <v>46259</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33661,7 +33661,7 @@
         <v>45526</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33739,7 +33739,7 @@
         <v>46258</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33812,7 +33812,7 @@
         <v>46258</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33885,7 +33885,7 @@
         <v>45432</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33958,7 +33958,7 @@
         <v>46261</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34036,7 +34036,7 @@
         <v>46261</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34114,7 +34114,7 @@
         <v>45636</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34187,7 +34187,7 @@
         <v>45644</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>45601</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44876</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34411,7 +34411,7 @@
         <v>46195</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>46262</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34562,7 +34562,7 @@
         <v>46266</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34635,7 +34635,7 @@
         <v>46225</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34708,7 +34708,7 @@
         <v>45463</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34781,7 +34781,7 @@
         <v>46225</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34854,7 +34854,7 @@
         <v>45029</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34927,7 +34927,7 @@
         <v>46225</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>46266</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35073,7 +35073,7 @@
         <v>46269</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>46268</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35224,7 +35224,7 @@
         <v>46269</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35302,7 +35302,7 @@
         <v>46269</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35380,7 +35380,7 @@
         <v>46273</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35453,7 +35453,7 @@
         <v>46268</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>45565</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35604,7 +35604,7 @@
         <v>46230</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>45627</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35750,7 +35750,7 @@
         <v>46269</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35828,7 +35828,7 @@
         <v>46269</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35906,7 +35906,7 @@
         <v>46273</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         <v>45215</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36052,7 +36052,7 @@
         <v>46279</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>46279</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36203,7 +36203,7 @@
         <v>46276</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36276,7 +36276,7 @@
         <v>46279</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>46279</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36432,7 +36432,7 @@
         <v>46276</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36510,7 +36510,7 @@
         <v>46280</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36588,7 +36588,7 @@
         <v>45049</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36661,7 +36661,7 @@
         <v>44901</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>46280</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36812,7 +36812,7 @@
         <v>45600</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36885,7 +36885,7 @@
         <v>46239</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36958,7 +36958,7 @@
         <v>46239</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37031,7 +37031,7 @@
         <v>45250</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
         <v>46240</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>45610</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37255,7 +37255,7 @@
         <v>46240</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>46240</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37401,7 +37401,7 @@
         <v>46239</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37474,7 +37474,7 @@
         <v>45583</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37547,7 +37547,7 @@
         <v>46282</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37625,7 +37625,7 @@
         <v>46239</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>46240</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37776,7 +37776,7 @@
         <v>46282</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37849,7 +37849,7 @@
         <v>46240</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37922,7 +37922,7 @@
         <v>46283</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38000,7 +38000,7 @@
         <v>44571</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38073,7 +38073,7 @@
         <v>44895</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>46240</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38219,7 +38219,7 @@
         <v>46240</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38292,7 +38292,7 @@
         <v>46286</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38370,7 +38370,7 @@
         <v>45468</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38443,7 +38443,7 @@
         <v>46185</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38516,7 +38516,7 @@
         <v>45545</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38589,7 +38589,7 @@
         <v>45664</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38662,7 +38662,7 @@
         <v>46286</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38740,7 +38740,7 @@
         <v>46244</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38813,7 +38813,7 @@
         <v>45708</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>46288</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38959,7 +38959,7 @@
         <v>45496</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39037,7 +39037,7 @@
         <v>44622</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39115,7 +39115,7 @@
         <v>46289</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39188,7 +39188,7 @@
         <v>45082</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39261,7 +39261,7 @@
         <v>45644</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39334,7 +39334,7 @@
         <v>46289</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39412,7 +39412,7 @@
         <v>44952</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39485,7 +39485,7 @@
         <v>46288</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39563,7 +39563,7 @@
         <v>44980</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39636,7 +39636,7 @@
         <v>46289</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39714,7 +39714,7 @@
         <v>46240</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39792,7 +39792,7 @@
         <v>46196</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>46291</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39943,7 +39943,7 @@
         <v>46188</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40016,7 +40016,7 @@
         <v>46291</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40094,7 +40094,7 @@
         <v>46132</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40172,7 +40172,7 @@
         <v>45708</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40245,7 +40245,7 @@
         <v>45184</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40323,7 +40323,7 @@
         <v>46191</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40401,7 +40401,7 @@
         <v>45607</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40474,7 +40474,7 @@
         <v>45659</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40547,7 +40547,7 @@
         <v>44980</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40620,7 +40620,7 @@
         <v>45182</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>45631</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>46297</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40844,7 +40844,7 @@
         <v>46297</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40922,7 +40922,7 @@
         <v>46297</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41000,7 +41000,7 @@
         <v>45135</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41078,7 +41078,7 @@
         <v>46297</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>46255</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>46255</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41302,7 +41302,7 @@
         <v>46254</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41375,7 +41375,7 @@
         <v>45636</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41448,7 +41448,7 @@
         <v>45040</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41521,7 +41521,7 @@
         <v>44683</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41599,7 +41599,7 @@
         <v>45530</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41672,7 +41672,7 @@
         <v>44960</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41745,7 +41745,7 @@
         <v>44588</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41818,7 +41818,7 @@
         <v>45659</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41891,7 +41891,7 @@
         <v>45525</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41964,7 +41964,7 @@
         <v>45692</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42037,7 +42037,7 @@
         <v>45671</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>44551</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42183,7 +42183,7 @@
         <v>44732</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42256,7 +42256,7 @@
         <v>44811</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42329,7 +42329,7 @@
         <v>44699</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42402,7 +42402,7 @@
         <v>44901</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>45005</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42548,7 +42548,7 @@
         <v>45148</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42626,7 +42626,7 @@
         <v>45670</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42699,7 +42699,7 @@
         <v>45687</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42772,7 +42772,7 @@
         <v>45701</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42845,7 +42845,7 @@
         <v>45161</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>45246</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42991,7 +42991,7 @@
         <v>45246</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43064,7 +43064,7 @@
         <v>45160</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43137,7 +43137,7 @@
         <v>45644</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43210,7 +43210,7 @@
         <v>45628</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43283,7 +43283,7 @@
         <v>44707</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43356,7 +43356,7 @@
         <v>44501</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43429,7 +43429,7 @@
         <v>45747</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43507,7 +43507,7 @@
         <v>45762</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43585,7 +43585,7 @@
         <v>46092</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>46147</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>46149</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43804,7 +43804,7 @@
         <v>46155</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>

--- a/Översikt ROBERTSFORS.xlsx
+++ b/Översikt ROBERTSFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46097</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45701</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44919</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45250</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45944</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>45936</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>44473</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>45939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>45792</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>46070</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>46135</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>45796</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45967</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>45153</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>46050</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45891</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>45915</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>45848</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>44725</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>45119</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>46037</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>44535</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>45560</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>45504</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>45051</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>46038</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>46050</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>46050</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>46050</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>45937</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>45177</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>45468</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>46265</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>45182</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>45182</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>44699</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>44559</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>44803</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>44497</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>45210</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>46050</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>46050</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>46050</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>45153</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>45233</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>45245</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>45827</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>45835</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>45510</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>44823</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>45844</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>45856</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>45146</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>45182</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>45124</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>45719</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>45957</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>45163</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         <v>45630</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>46198</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>46204</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>45245</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>46269</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>45695</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>45712</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>45176</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>44312</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>45747</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>45919</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>44784</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8393,7 +8393,7 @@
         <v>44810</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>44677</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>44880</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>44734</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>44734</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>44858</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>44645</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>44572</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>44497</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>44721</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>44658</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>44612</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>44612</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>44641</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>44775</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>44575</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         <v>44735</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9644,7 +9644,7 @@
         <v>44795</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
         <v>44855</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>44612</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>44473</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         <v>44519</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>44571</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>44473</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
         <v>44532</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>44844</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>44482</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10384,7 +10384,7 @@
         <v>44612</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10457,7 +10457,7 @@
         <v>44612</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         <v>44851</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>44729</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>44819</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>44662</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>44697</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>44812</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>44827</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>44841</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>44824</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>44475</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>44580</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>44574</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>44641</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>44644</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>44817</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>44615</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>44488</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>44627</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>44627</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>44789</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>45687</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12088,7 +12088,7 @@
         <v>45246</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>45625</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>45079</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>45033</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>45474</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>45537</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>45537</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>45048</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>45548</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>45197</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>45700</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         <v>45580</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12989,7 +12989,7 @@
         <v>45622</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>45617</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13135,7 +13135,7 @@
         <v>45253</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>45405</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
         <v>45019</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>45184</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>45495</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>45642</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>45496</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>45553</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         <v>45484</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13802,7 +13802,7 @@
         <v>45572</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         <v>45188</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13948,7 +13948,7 @@
         <v>45559</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>45559</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>45889</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>45890</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>44894</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>45890</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>45895</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>45893</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>45896</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>45659</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>45461</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         <v>46037</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>45541</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14922,7 +14922,7 @@
         <v>45468</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>45909</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15068,7 +15068,7 @@
         <v>46042</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15141,7 +15141,7 @@
         <v>45540</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>44904</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>46042</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>45715</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15438,7 +15438,7 @@
         <v>45915</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15516,7 +15516,7 @@
         <v>45794</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>45761</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>46048</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15735,7 +15735,7 @@
         <v>45446</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>45800</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>46050</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>45918</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>45800</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
         <v>45919</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>45803</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
         <v>44960</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16324,7 +16324,7 @@
         <v>44960</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16397,7 +16397,7 @@
         <v>46050</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>45803</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16543,7 +16543,7 @@
         <v>46050</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16616,7 +16616,7 @@
         <v>45924</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>44913</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45070</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>46058</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>45926</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>45929</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>46059</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>46059</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>45251</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>46063</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>46065</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>44902</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>45197</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17590,7 +17590,7 @@
         <v>46065</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17663,7 +17663,7 @@
         <v>45030</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17736,7 +17736,7 @@
         <v>44860</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17809,7 +17809,7 @@
         <v>45687</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>45251</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>45938</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>45695</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>45033</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18179,7 +18179,7 @@
         <v>45678</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18257,7 +18257,7 @@
         <v>44805</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>45610</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>45636</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>45687</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18554,7 +18554,7 @@
         <v>46076</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>45782</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>45090</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>45202</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18846,7 +18846,7 @@
         <v>44953</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>46083</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18992,7 +18992,7 @@
         <v>45957</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>45149</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>45813</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>45957</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19289,7 +19289,7 @@
         <v>45958</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>45959</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>45458</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>45959</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>45960</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19669,7 +19669,7 @@
         <v>45961</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>45205</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19820,7 +19820,7 @@
         <v>45965</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>45965</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>45581</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20039,7 +20039,7 @@
         <v>45965</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>46094</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20190,7 +20190,7 @@
         <v>45617</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>45966</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20346,7 +20346,7 @@
         <v>45965</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20419,7 +20419,7 @@
         <v>45715</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20497,7 +20497,7 @@
         <v>45458</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20570,7 +20570,7 @@
         <v>45635</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20643,7 +20643,7 @@
         <v>46099</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20716,7 +20716,7 @@
         <v>46099</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20789,7 +20789,7 @@
         <v>46104</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>45974</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20940,7 +20940,7 @@
         <v>45029</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21013,7 +21013,7 @@
         <v>46105</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21086,7 +21086,7 @@
         <v>45818</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21159,7 +21159,7 @@
         <v>45981</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21237,7 +21237,7 @@
         <v>44516</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21310,7 +21310,7 @@
         <v>45981</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21388,7 +21388,7 @@
         <v>45981</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>45480</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         <v>45661</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>45664</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
         <v>44516</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21753,7 +21753,7 @@
         <v>46112</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21826,7 +21826,7 @@
         <v>45281</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21899,7 +21899,7 @@
         <v>45987</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21972,7 +21972,7 @@
         <v>45191</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>45512</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22118,7 +22118,7 @@
         <v>44783</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22191,7 +22191,7 @@
         <v>44838</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>45162</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22337,7 +22337,7 @@
         <v>45653</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22410,7 +22410,7 @@
         <v>44938</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>46122</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22556,7 +22556,7 @@
         <v>46122</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22629,7 +22629,7 @@
         <v>44945</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22702,7 +22702,7 @@
         <v>44487</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22780,7 +22780,7 @@
         <v>46126</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22853,7 +22853,7 @@
         <v>46126</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22926,7 +22926,7 @@
         <v>46126</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22999,7 +22999,7 @@
         <v>45996</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23072,7 +23072,7 @@
         <v>45544</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23150,7 +23150,7 @@
         <v>45831</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>45701</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>46000</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23369,7 +23369,7 @@
         <v>46000</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23447,7 +23447,7 @@
         <v>44901</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23520,7 +23520,7 @@
         <v>46132</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>45832</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23676,7 +23676,7 @@
         <v>46135</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23749,7 +23749,7 @@
         <v>46135</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23822,7 +23822,7 @@
         <v>45335</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23895,7 +23895,7 @@
         <v>45671</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23968,7 +23968,7 @@
         <v>46135</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>46135</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24114,7 +24114,7 @@
         <v>45502</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24187,7 +24187,7 @@
         <v>45839</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24260,7 +24260,7 @@
         <v>45474</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24338,7 +24338,7 @@
         <v>45839</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>45839</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>45839</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24557,7 +24557,7 @@
         <v>45839</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>45145</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>45839</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24781,7 +24781,7 @@
         <v>45405</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24854,7 +24854,7 @@
         <v>45090</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24927,7 +24927,7 @@
         <v>45841</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         <v>45841</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>45005</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25146,7 +25146,7 @@
         <v>44580</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25219,7 +25219,7 @@
         <v>45020</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25297,7 +25297,7 @@
         <v>45826</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25370,7 +25370,7 @@
         <v>44502</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25443,7 +25443,7 @@
         <v>45930</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25516,7 +25516,7 @@
         <v>46139</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25589,7 +25589,7 @@
         <v>45901</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25667,7 +25667,7 @@
         <v>45929</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25745,7 +25745,7 @@
         <v>45734</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>45856</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>45856</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25964,7 +25964,7 @@
         <v>45856</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26037,7 +26037,7 @@
         <v>45789</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>45561</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26183,7 +26183,7 @@
         <v>45246</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26256,7 +26256,7 @@
         <v>46140</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26334,7 +26334,7 @@
         <v>45251</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26412,7 +26412,7 @@
         <v>45510</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>45246</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26563,7 +26563,7 @@
         <v>45365</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>45162</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>45357</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26782,7 +26782,7 @@
         <v>45712</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         <v>45628</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>45587</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         <v>45238</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>45146</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>45870</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>45013</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>44973</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>46146</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27454,7 +27454,7 @@
         <v>45042</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27527,7 +27527,7 @@
         <v>45679</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27600,7 +27600,7 @@
         <v>46146</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27673,7 +27673,7 @@
         <v>46148</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27746,7 +27746,7 @@
         <v>45141</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>45664</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>46153</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>46150</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>46153</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>46153</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>46153</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>44936</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>44734</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>46155</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>45205</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28569,7 +28569,7 @@
         <v>45076</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28642,7 +28642,7 @@
         <v>45502</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28715,7 +28715,7 @@
         <v>45020</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28793,7 +28793,7 @@
         <v>46160</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28866,7 +28866,7 @@
         <v>44475</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>46160</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>45873</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29085,7 +29085,7 @@
         <v>46160</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29163,7 +29163,7 @@
         <v>45580</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29236,7 +29236,7 @@
         <v>44980</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29314,7 +29314,7 @@
         <v>45002</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29387,7 +29387,7 @@
         <v>46171</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29460,7 +29460,7 @@
         <v>46170</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29533,7 +29533,7 @@
         <v>45129</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29606,7 +29606,7 @@
         <v>45182</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29679,7 +29679,7 @@
         <v>45386</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29752,7 +29752,7 @@
         <v>45090</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29825,7 +29825,7 @@
         <v>46171</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29898,7 +29898,7 @@
         <v>46175</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29971,7 +29971,7 @@
         <v>46176</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30044,7 +30044,7 @@
         <v>46113</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30117,7 +30117,7 @@
         <v>45454</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30190,7 +30190,7 @@
         <v>45404</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30263,7 +30263,7 @@
         <v>45610</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30341,7 +30341,7 @@
         <v>45302</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30414,7 +30414,7 @@
         <v>46177</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30487,7 +30487,7 @@
         <v>45611</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>46181</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30633,7 +30633,7 @@
         <v>45475</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>45160</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30784,7 +30784,7 @@
         <v>45635</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>46183</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>46185</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31003,7 +31003,7 @@
         <v>46185</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31076,7 +31076,7 @@
         <v>45458</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>46188</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31222,7 +31222,7 @@
         <v>46188</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>46188</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31368,7 +31368,7 @@
         <v>46185</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>45041</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31519,7 +31519,7 @@
         <v>45133</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31597,7 +31597,7 @@
         <v>45756</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31670,7 +31670,7 @@
         <v>45620</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31743,7 +31743,7 @@
         <v>45678</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31821,7 +31821,7 @@
         <v>45551</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31894,7 +31894,7 @@
         <v>46198</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31967,7 +31967,7 @@
         <v>45268</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32040,7 +32040,7 @@
         <v>45307</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>45607</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32186,7 +32186,7 @@
         <v>45470</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32259,7 +32259,7 @@
         <v>45301</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32332,7 +32332,7 @@
         <v>45712</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32405,7 +32405,7 @@
         <v>46202</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32478,7 +32478,7 @@
         <v>46204</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32556,7 +32556,7 @@
         <v>45261</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32629,7 +32629,7 @@
         <v>46203</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32702,7 +32702,7 @@
         <v>45617</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         <v>45160</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32848,7 +32848,7 @@
         <v>46206</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32921,7 +32921,7 @@
         <v>46205</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32994,7 +32994,7 @@
         <v>46205</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33067,7 +33067,7 @@
         <v>45176</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33140,7 +33140,7 @@
         <v>45365</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33213,7 +33213,7 @@
         <v>45548</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33286,7 +33286,7 @@
         <v>45568</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33359,7 +33359,7 @@
         <v>45667</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>45610</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33515,7 +33515,7 @@
         <v>44580</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33588,7 +33588,7 @@
         <v>46259</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33661,7 +33661,7 @@
         <v>45526</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33739,7 +33739,7 @@
         <v>46258</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33812,7 +33812,7 @@
         <v>46258</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33885,7 +33885,7 @@
         <v>45432</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33958,7 +33958,7 @@
         <v>46261</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34036,7 +34036,7 @@
         <v>46261</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34114,7 +34114,7 @@
         <v>45636</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34187,7 +34187,7 @@
         <v>45644</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>45601</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44876</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34411,7 +34411,7 @@
         <v>46195</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>46262</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34562,7 +34562,7 @@
         <v>46266</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34635,7 +34635,7 @@
         <v>46225</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34708,7 +34708,7 @@
         <v>45463</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34781,7 +34781,7 @@
         <v>46225</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34854,7 +34854,7 @@
         <v>45029</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34927,7 +34927,7 @@
         <v>46225</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>46266</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35073,7 +35073,7 @@
         <v>46269</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>46268</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35224,7 +35224,7 @@
         <v>46269</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35302,7 +35302,7 @@
         <v>46269</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35380,7 +35380,7 @@
         <v>46273</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35453,7 +35453,7 @@
         <v>46268</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>45565</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35604,7 +35604,7 @@
         <v>46230</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>45627</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35750,7 +35750,7 @@
         <v>46269</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35828,7 +35828,7 @@
         <v>46269</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35906,7 +35906,7 @@
         <v>46273</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         <v>45215</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36052,7 +36052,7 @@
         <v>46279</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>46279</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36203,7 +36203,7 @@
         <v>46276</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36276,7 +36276,7 @@
         <v>46279</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>46279</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36432,7 +36432,7 @@
         <v>46276</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36510,7 +36510,7 @@
         <v>46280</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36588,7 +36588,7 @@
         <v>45049</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36661,7 +36661,7 @@
         <v>44901</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>46280</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36812,7 +36812,7 @@
         <v>45600</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36885,7 +36885,7 @@
         <v>46239</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36958,7 +36958,7 @@
         <v>46239</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37031,7 +37031,7 @@
         <v>45250</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
         <v>46240</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>45610</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37255,7 +37255,7 @@
         <v>46240</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>46240</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37401,7 +37401,7 @@
         <v>46239</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37474,7 +37474,7 @@
         <v>45583</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37547,7 +37547,7 @@
         <v>46282</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37625,7 +37625,7 @@
         <v>46239</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>46240</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37776,7 +37776,7 @@
         <v>46282</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37849,7 +37849,7 @@
         <v>46240</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37922,7 +37922,7 @@
         <v>46283</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38000,7 +38000,7 @@
         <v>44571</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38073,7 +38073,7 @@
         <v>44895</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38146,7 +38146,7 @@
         <v>46240</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38219,7 +38219,7 @@
         <v>46240</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38292,7 +38292,7 @@
         <v>46286</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38370,7 +38370,7 @@
         <v>45468</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38443,7 +38443,7 @@
         <v>46185</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38516,7 +38516,7 @@
         <v>45545</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38589,7 +38589,7 @@
         <v>45664</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38662,7 +38662,7 @@
         <v>46286</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38740,7 +38740,7 @@
         <v>46244</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38813,7 +38813,7 @@
         <v>45708</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>46288</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38959,7 +38959,7 @@
         <v>45496</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39037,7 +39037,7 @@
         <v>44622</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39115,7 +39115,7 @@
         <v>46289</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39188,7 +39188,7 @@
         <v>45082</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39261,7 +39261,7 @@
         <v>45644</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39334,7 +39334,7 @@
         <v>46289</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39412,7 +39412,7 @@
         <v>44952</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39485,7 +39485,7 @@
         <v>46288</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39563,7 +39563,7 @@
         <v>44980</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39636,7 +39636,7 @@
         <v>46289</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39714,7 +39714,7 @@
         <v>46240</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39792,7 +39792,7 @@
         <v>46196</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>46291</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39943,7 +39943,7 @@
         <v>46188</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40016,7 +40016,7 @@
         <v>46291</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40094,7 +40094,7 @@
         <v>46132</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40172,7 +40172,7 @@
         <v>45708</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40245,7 +40245,7 @@
         <v>45184</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40323,7 +40323,7 @@
         <v>46191</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40401,7 +40401,7 @@
         <v>45607</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40474,7 +40474,7 @@
         <v>45659</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40547,7 +40547,7 @@
         <v>44980</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40620,7 +40620,7 @@
         <v>45182</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>45631</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>46297</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40844,7 +40844,7 @@
         <v>46297</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40922,7 +40922,7 @@
         <v>46297</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41000,7 +41000,7 @@
         <v>45135</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41078,7 +41078,7 @@
         <v>46297</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>46255</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>46255</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41302,7 +41302,7 @@
         <v>46254</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41375,7 +41375,7 @@
         <v>45636</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41448,7 +41448,7 @@
         <v>45040</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41521,7 +41521,7 @@
         <v>44683</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41599,7 +41599,7 @@
         <v>45530</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41672,7 +41672,7 @@
         <v>44960</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41745,7 +41745,7 @@
         <v>44588</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41818,7 +41818,7 @@
         <v>45659</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41891,7 +41891,7 @@
         <v>45525</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41964,7 +41964,7 @@
         <v>45692</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42037,7 +42037,7 @@
         <v>45671</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>44551</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42183,7 +42183,7 @@
         <v>44732</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42256,7 +42256,7 @@
         <v>44811</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42329,7 +42329,7 @@
         <v>44699</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42402,7 +42402,7 @@
         <v>44901</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>45005</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42548,7 +42548,7 @@
         <v>45148</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42626,7 +42626,7 @@
         <v>45670</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42699,7 +42699,7 @@
         <v>45687</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42772,7 +42772,7 @@
         <v>45701</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42845,7 +42845,7 @@
         <v>45161</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>45246</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42991,7 +42991,7 @@
         <v>45246</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43064,7 +43064,7 @@
         <v>45160</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43137,7 +43137,7 @@
         <v>45644</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43210,7 +43210,7 @@
         <v>45628</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43283,7 +43283,7 @@
         <v>44707</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43356,7 +43356,7 @@
         <v>44501</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43429,7 +43429,7 @@
         <v>45747</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43507,7 +43507,7 @@
         <v>45762</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43585,7 +43585,7 @@
         <v>46092</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>46147</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>46149</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43804,7 +43804,7 @@
         <v>46155</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>

--- a/Översikt ROBERTSFORS.xlsx
+++ b/Översikt ROBERTSFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46097</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45701</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44919</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45250</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45944</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>45936</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>45939</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>45792</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>46070</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>46135</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>45796</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>45967</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>45153</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>46050</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>45891</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45119</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>45915</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>45848</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>44725</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>46037</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>44535</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>45504</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>45177</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>45182</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>45937</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>45051</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>45468</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>45182</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>46038</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>45560</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>46050</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>46050</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>46050</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>46265</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>44699</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>44559</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>44803</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>44497</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         <v>45210</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>45510</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>45124</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>44823</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>45233</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>45153</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>45630</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>45712</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>45146</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>45827</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>45245</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>45835</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>45844</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>45245</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>45163</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>45176</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>45695</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         <v>45182</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>45856</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>46050</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>46050</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>46050</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>45719</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>45957</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
         <v>46198</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>46204</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>46269</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>44312</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         <v>45747</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>45919</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8198,7 +8198,7 @@
         <v>44784</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>44810</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>44677</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>44880</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>44734</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>44734</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>44858</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>44645</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>44572</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>44497</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>44721</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>44658</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>44612</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>44612</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>44641</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>44775</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>44575</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>44795</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         <v>44735</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         <v>44612</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>44855</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
         <v>44851</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>44824</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>44697</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>44519</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>44571</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>44812</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>44580</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>44729</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>44574</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>44532</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>44844</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>44827</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>44641</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10720,7 +10720,7 @@
         <v>44482</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10793,7 +10793,7 @@
         <v>44841</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
         <v>44612</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>44612</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>44819</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>44644</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>44662</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11236,7 +11236,7 @@
         <v>44817</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         <v>44615</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>44488</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>44627</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>44627</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11601,7 +11601,7 @@
         <v>44789</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
         <v>45160</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>45070</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>45042</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>45090</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>45250</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>44901</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>45090</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>45715</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>44895</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         <v>44904</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12409,7 +12409,7 @@
         <v>45695</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12482,7 +12482,7 @@
         <v>45268</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12555,7 +12555,7 @@
         <v>44980</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>45253</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>45135</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12779,7 +12779,7 @@
         <v>45617</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12852,7 +12852,7 @@
         <v>45617</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12930,7 +12930,7 @@
         <v>44945</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13003,7 +13003,7 @@
         <v>45526</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13081,7 +13081,7 @@
         <v>45461</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
         <v>45029</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>45530</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>44953</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13373,7 +13373,7 @@
         <v>45307</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>45197</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>45664</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>45659</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>44571</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>45587</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>44902</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
         <v>44860</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13967,7 +13967,7 @@
         <v>45251</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14045,7 +14045,7 @@
         <v>45551</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14118,7 +14118,7 @@
         <v>45458</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14191,7 +14191,7 @@
         <v>45148</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>45544</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>44973</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         <v>45405</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>45525</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>44901</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>45162</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>45365</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         <v>45019</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>45610</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14936,7 +14936,7 @@
         <v>45568</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>45572</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>45365</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>45610</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         <v>45049</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>45889</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15379,7 +15379,7 @@
         <v>44980</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15452,7 +15452,7 @@
         <v>45890</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15530,7 +15530,7 @@
         <v>45890</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>45020</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15686,7 +15686,7 @@
         <v>45496</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15764,7 +15764,7 @@
         <v>45893</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
         <v>45895</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>45896</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>45215</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>45687</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>45545</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16207,7 +16207,7 @@
         <v>45480</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>45635</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>45141</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>45281</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>45628</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>45468</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16650,7 +16650,7 @@
         <v>45475</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>45251</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>45631</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>44487</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>45610</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17025,7 +17025,7 @@
         <v>45541</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17103,7 +17103,7 @@
         <v>45540</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17181,7 +17181,7 @@
         <v>44913</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         <v>45149</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17332,7 +17332,7 @@
         <v>45162</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>45644</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>45628</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>45160</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17624,7 +17624,7 @@
         <v>45909</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>45474</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>45161</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>44876</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>45246</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17994,7 +17994,7 @@
         <v>45246</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18067,7 +18067,7 @@
         <v>45246</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18140,7 +18140,7 @@
         <v>45458</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18213,7 +18213,7 @@
         <v>45160</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>45915</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>44551</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>45484</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>44894</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>44901</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18656,7 +18656,7 @@
         <v>45357</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>45918</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>45041</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>45302</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>45583</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>45617</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19099,7 +19099,7 @@
         <v>45405</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>45919</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>45005</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>45924</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19396,7 +19396,7 @@
         <v>45642</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>45495</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19547,7 +19547,7 @@
         <v>45926</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>45335</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
         <v>45082</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19771,7 +19771,7 @@
         <v>45712</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>45512</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>45678</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         <v>45030</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20068,7 +20068,7 @@
         <v>45188</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20141,7 +20141,7 @@
         <v>45636</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>45182</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>45929</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20365,7 +20365,7 @@
         <v>45794</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
         <v>45496</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>45553</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>45701</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>45191</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>45404</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>44580</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>45761</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20954,7 +20954,7 @@
         <v>45627</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21027,7 +21027,7 @@
         <v>45800</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>45679</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21173,7 +21173,7 @@
         <v>45800</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>45610</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>44683</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>45548</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>45803</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>45803</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>45625</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>44732</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>45938</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>45601</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>44805</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21991,7 +21991,7 @@
         <v>45687</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>45600</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22137,7 +22137,7 @@
         <v>45184</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22215,7 +22215,7 @@
         <v>45246</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22288,7 +22288,7 @@
         <v>45636</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22361,7 +22361,7 @@
         <v>45687</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22434,7 +22434,7 @@
         <v>45559</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>45708</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         <v>44588</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>44622</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>45782</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22809,7 +22809,7 @@
         <v>45653</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>45664</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>45712</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>45251</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23106,7 +23106,7 @@
         <v>45559</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23179,7 +23179,7 @@
         <v>45607</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>45813</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23325,7 +23325,7 @@
         <v>44699</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>45818</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>45671</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>45659</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>44960</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23690,7 +23690,7 @@
         <v>44960</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>44960</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>45079</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>45565</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>45611</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>45020</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24133,7 +24133,7 @@
         <v>45670</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>44952</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24279,7 +24279,7 @@
         <v>44838</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24352,7 +24352,7 @@
         <v>45446</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24425,7 +24425,7 @@
         <v>44516</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24498,7 +24498,7 @@
         <v>45090</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24571,7 +24571,7 @@
         <v>45700</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24644,7 +24644,7 @@
         <v>45832</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>45831</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>45205</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>45957</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>45958</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25019,7 +25019,7 @@
         <v>45957</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>45959</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25170,7 +25170,7 @@
         <v>45959</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25243,7 +25243,7 @@
         <v>45202</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>45474</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25394,7 +25394,7 @@
         <v>45960</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25472,7 +25472,7 @@
         <v>45961</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>45839</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>45965</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>45966</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25774,7 +25774,7 @@
         <v>45965</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25847,7 +25847,7 @@
         <v>45839</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25920,7 +25920,7 @@
         <v>45839</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25993,7 +25993,7 @@
         <v>45839</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26066,7 +26066,7 @@
         <v>45839</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26139,7 +26139,7 @@
         <v>45839</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26212,7 +26212,7 @@
         <v>45715</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26290,7 +26290,7 @@
         <v>45965</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26363,7 +26363,7 @@
         <v>45659</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26436,7 +26436,7 @@
         <v>45965</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26509,7 +26509,7 @@
         <v>45841</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>45667</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>45841</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26733,7 +26733,7 @@
         <v>45661</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26806,7 +26806,7 @@
         <v>45664</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26879,7 +26879,7 @@
         <v>45184</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26952,7 +26952,7 @@
         <v>45635</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27025,7 +27025,7 @@
         <v>45033</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>45708</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27171,7 +27171,7 @@
         <v>45756</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27244,7 +27244,7 @@
         <v>44783</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27317,7 +27317,7 @@
         <v>45974</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27395,7 +27395,7 @@
         <v>45644</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>45463</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27541,7 +27541,7 @@
         <v>45856</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27614,7 +27614,7 @@
         <v>45458</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27687,7 +27687,7 @@
         <v>45856</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27760,7 +27760,7 @@
         <v>45856</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27833,7 +27833,7 @@
         <v>45789</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>45205</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27979,7 +27979,7 @@
         <v>45301</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28052,7 +28052,7 @@
         <v>45692</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28125,7 +28125,7 @@
         <v>45182</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28198,7 +28198,7 @@
         <v>45197</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28276,7 +28276,7 @@
         <v>45701</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>45870</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>45040</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28495,7 +28495,7 @@
         <v>45013</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28568,7 +28568,7 @@
         <v>45176</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28641,7 +28641,7 @@
         <v>45873</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28714,7 +28714,7 @@
         <v>45687</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>45005</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28860,7 +28860,7 @@
         <v>45981</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28933,7 +28933,7 @@
         <v>45981</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29011,7 +29011,7 @@
         <v>45981</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29089,7 +29089,7 @@
         <v>45537</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29167,7 +29167,7 @@
         <v>45636</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         <v>44938</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29313,7 +29313,7 @@
         <v>45261</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29386,7 +29386,7 @@
         <v>46094</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29464,7 +29464,7 @@
         <v>46099</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>46099</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29610,7 +29610,7 @@
         <v>45002</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29683,7 +29683,7 @@
         <v>45468</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>46104</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29829,7 +29829,7 @@
         <v>45537</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>45644</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29980,7 +29980,7 @@
         <v>46105</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30053,7 +30053,7 @@
         <v>45133</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30131,7 +30131,7 @@
         <v>45510</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30209,7 +30209,7 @@
         <v>45622</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30282,7 +30282,7 @@
         <v>45671</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30355,7 +30355,7 @@
         <v>44980</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30433,7 +30433,7 @@
         <v>45987</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30506,7 +30506,7 @@
         <v>45581</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>45548</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>46122</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>44516</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30798,7 +30798,7 @@
         <v>46126</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30871,7 +30871,7 @@
         <v>45996</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30944,7 +30944,7 @@
         <v>46126</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31017,7 +31017,7 @@
         <v>46000</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>45033</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31168,7 +31168,7 @@
         <v>45048</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31241,7 +31241,7 @@
         <v>46126</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31314,7 +31314,7 @@
         <v>46000</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>44936</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31460,7 +31460,7 @@
         <v>46132</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31538,7 +31538,7 @@
         <v>45432</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31611,7 +31611,7 @@
         <v>44811</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31684,7 +31684,7 @@
         <v>46135</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31757,7 +31757,7 @@
         <v>46135</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31830,7 +31830,7 @@
         <v>46135</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31903,7 +31903,7 @@
         <v>45607</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31976,7 +31976,7 @@
         <v>44502</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32049,7 +32049,7 @@
         <v>44580</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32122,7 +32122,7 @@
         <v>46135</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32195,7 +32195,7 @@
         <v>45901</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32273,7 +32273,7 @@
         <v>45734</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>45246</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>45580</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32497,7 +32497,7 @@
         <v>45502</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32570,7 +32570,7 @@
         <v>46139</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32643,7 +32643,7 @@
         <v>45561</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32716,7 +32716,7 @@
         <v>45238</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32789,7 +32789,7 @@
         <v>46140</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>45470</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32940,7 +32940,7 @@
         <v>46037</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33013,7 +33013,7 @@
         <v>45029</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33086,7 +33086,7 @@
         <v>46042</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33159,7 +33159,7 @@
         <v>45145</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33237,7 +33237,7 @@
         <v>45929</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33315,7 +33315,7 @@
         <v>44734</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33388,7 +33388,7 @@
         <v>45826</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33461,7 +33461,7 @@
         <v>45076</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33534,7 +33534,7 @@
         <v>46048</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33607,7 +33607,7 @@
         <v>45146</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>45930</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>45129</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33831,7 +33831,7 @@
         <v>46050</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33904,7 +33904,7 @@
         <v>46050</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33977,7 +33977,7 @@
         <v>46050</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>46058</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34128,7 +34128,7 @@
         <v>46059</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34201,7 +34201,7 @@
         <v>46059</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34274,7 +34274,7 @@
         <v>46063</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34347,7 +34347,7 @@
         <v>46146</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34425,7 +34425,7 @@
         <v>46146</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>46065</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34571,7 +34571,7 @@
         <v>46148</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34644,7 +34644,7 @@
         <v>46065</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34717,7 +34717,7 @@
         <v>46150</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34795,7 +34795,7 @@
         <v>45678</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34873,7 +34873,7 @@
         <v>46153</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34946,7 +34946,7 @@
         <v>46076</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>46153</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35097,7 +35097,7 @@
         <v>46153</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35170,7 +35170,7 @@
         <v>46153</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35248,7 +35248,7 @@
         <v>46083</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35321,7 +35321,7 @@
         <v>46155</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35394,7 +35394,7 @@
         <v>46160</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35472,7 +35472,7 @@
         <v>46160</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35545,7 +35545,7 @@
         <v>46160</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35618,7 +35618,7 @@
         <v>45502</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35691,7 +35691,7 @@
         <v>45580</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35764,7 +35764,7 @@
         <v>45386</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>46171</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35910,7 +35910,7 @@
         <v>46170</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35983,7 +35983,7 @@
         <v>46171</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36056,7 +36056,7 @@
         <v>46176</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36129,7 +36129,7 @@
         <v>46175</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>46177</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36275,7 +36275,7 @@
         <v>45454</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>46113</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36421,7 +36421,7 @@
         <v>46181</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36494,7 +36494,7 @@
         <v>46183</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36567,7 +36567,7 @@
         <v>46185</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36640,7 +36640,7 @@
         <v>46185</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36713,7 +36713,7 @@
         <v>46185</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36791,7 +36791,7 @@
         <v>46188</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36864,7 +36864,7 @@
         <v>46188</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36937,7 +36937,7 @@
         <v>46188</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>45620</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37083,7 +37083,7 @@
         <v>46198</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37156,7 +37156,7 @@
         <v>46202</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>46203</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37302,7 +37302,7 @@
         <v>46204</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37380,7 +37380,7 @@
         <v>46205</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>46205</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37526,7 +37526,7 @@
         <v>46206</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37599,7 +37599,7 @@
         <v>46266</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37672,7 +37672,7 @@
         <v>46266</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37745,7 +37745,7 @@
         <v>46195</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>46225</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>46268</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37964,7 +37964,7 @@
         <v>46225</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38037,7 +38037,7 @@
         <v>46225</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>46269</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38188,7 +38188,7 @@
         <v>46269</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38266,7 +38266,7 @@
         <v>46269</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38344,7 +38344,7 @@
         <v>46268</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38422,7 +38422,7 @@
         <v>46269</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38500,7 +38500,7 @@
         <v>46269</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38578,7 +38578,7 @@
         <v>46273</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38651,7 +38651,7 @@
         <v>46273</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38724,7 +38724,7 @@
         <v>46230</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38797,7 +38797,7 @@
         <v>46276</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38870,7 +38870,7 @@
         <v>46276</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38948,7 +38948,7 @@
         <v>46279</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39021,7 +39021,7 @@
         <v>46279</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39099,7 +39099,7 @@
         <v>46280</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39177,7 +39177,7 @@
         <v>46280</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39255,7 +39255,7 @@
         <v>46279</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39333,7 +39333,7 @@
         <v>46279</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39411,7 +39411,7 @@
         <v>46239</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39484,7 +39484,7 @@
         <v>46282</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39557,7 +39557,7 @@
         <v>46240</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39630,7 +39630,7 @@
         <v>46282</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39708,7 +39708,7 @@
         <v>46239</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>46240</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>46240</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39927,7 +39927,7 @@
         <v>46240</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40000,7 +40000,7 @@
         <v>46239</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40073,7 +40073,7 @@
         <v>46283</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40151,7 +40151,7 @@
         <v>46240</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>46185</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40297,7 +40297,7 @@
         <v>46240</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40375,7 +40375,7 @@
         <v>46240</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40448,7 +40448,7 @@
         <v>46286</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40526,7 +40526,7 @@
         <v>46286</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40604,7 +40604,7 @@
         <v>46288</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40677,7 +40677,7 @@
         <v>46244</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>46288</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40828,7 +40828,7 @@
         <v>46188</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40901,7 +40901,7 @@
         <v>46191</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40979,7 +40979,7 @@
         <v>46196</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41052,7 +41052,7 @@
         <v>46289</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41130,7 +41130,7 @@
         <v>46240</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41208,7 +41208,7 @@
         <v>46289</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41281,7 +41281,7 @@
         <v>46132</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41359,7 +41359,7 @@
         <v>46289</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41437,7 +41437,7 @@
         <v>46291</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41515,7 +41515,7 @@
         <v>46291</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41593,7 +41593,7 @@
         <v>46297</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41671,7 +41671,7 @@
         <v>46254</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41744,7 +41744,7 @@
         <v>46297</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41822,7 +41822,7 @@
         <v>46297</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41900,7 +41900,7 @@
         <v>46297</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41978,7 +41978,7 @@
         <v>46255</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>46255</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42124,7 +42124,7 @@
         <v>46259</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42197,7 +42197,7 @@
         <v>46112</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42270,7 +42270,7 @@
         <v>46302</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42343,7 +42343,7 @@
         <v>46258</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42416,7 +42416,7 @@
         <v>46258</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42489,7 +42489,7 @@
         <v>46261</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42567,7 +42567,7 @@
         <v>46262</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42645,7 +42645,7 @@
         <v>46239</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42718,7 +42718,7 @@
         <v>46261</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42796,7 +42796,7 @@
         <v>46303</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42874,7 +42874,7 @@
         <v>46303</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42947,7 +42947,7 @@
         <v>44707</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43020,7 +43020,7 @@
         <v>44501</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43093,7 +43093,7 @@
         <v>45747</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43171,7 +43171,7 @@
         <v>45762</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43249,7 +43249,7 @@
         <v>46092</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43322,7 +43322,7 @@
         <v>46147</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43395,7 +43395,7 @@
         <v>46149</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43468,7 +43468,7 @@
         <v>46155</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>

--- a/Översikt ROBERTSFORS.xlsx
+++ b/Översikt ROBERTSFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46097</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45701</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44919</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45250</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45944</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>45936</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>45939</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>45792</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>46070</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>46135</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>45796</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>45967</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>45153</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>46050</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>45891</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45119</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>45915</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>45848</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>44725</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>46037</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>44535</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>45504</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>45177</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>45182</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>45937</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>45051</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>45468</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>45182</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>46038</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>45560</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>46050</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>46050</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>46050</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>46265</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>44699</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>44559</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>44803</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>44497</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         <v>45210</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>45510</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>45124</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>44823</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>45233</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>45153</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>45630</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>45712</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>45146</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>45827</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>45245</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>45835</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>45844</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>45245</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>45163</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>45176</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>45695</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         <v>45182</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>45856</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>46050</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>46050</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>46050</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>45719</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>45957</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
         <v>46198</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>46204</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>46269</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>44312</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         <v>45747</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>45919</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8198,7 +8198,7 @@
         <v>44784</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>44810</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>44677</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>44880</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>44734</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>44734</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>44858</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>44645</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>44572</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>44497</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>44721</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>44658</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>44612</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>44612</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>44641</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>44775</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>44575</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>44795</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         <v>44735</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         <v>44612</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>44855</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
         <v>44851</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>44824</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>44697</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>44519</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>44571</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>44812</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>44580</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>44729</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>44574</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>44532</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>44844</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>44827</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>44641</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10720,7 +10720,7 @@
         <v>44482</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10793,7 +10793,7 @@
         <v>44841</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
         <v>44612</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>44612</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>44819</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>44644</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>44662</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11236,7 +11236,7 @@
         <v>44817</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         <v>44615</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>44488</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>44627</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>44627</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11601,7 +11601,7 @@
         <v>44789</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
         <v>45160</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>45070</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>45042</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>45090</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>45250</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>44901</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>45090</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>45715</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>44895</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         <v>44904</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12409,7 +12409,7 @@
         <v>45695</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12482,7 +12482,7 @@
         <v>45268</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12555,7 +12555,7 @@
         <v>44980</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>45253</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>45135</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12779,7 +12779,7 @@
         <v>45617</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12852,7 +12852,7 @@
         <v>45617</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12930,7 +12930,7 @@
         <v>44945</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13003,7 +13003,7 @@
         <v>45526</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13081,7 +13081,7 @@
         <v>45461</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
         <v>45029</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>45530</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>44953</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13373,7 +13373,7 @@
         <v>45307</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>45197</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>45664</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>45659</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>44571</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>45587</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>44902</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
         <v>44860</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13967,7 +13967,7 @@
         <v>45251</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14045,7 +14045,7 @@
         <v>45551</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14118,7 +14118,7 @@
         <v>45458</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14191,7 +14191,7 @@
         <v>45148</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>45544</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>44973</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         <v>45405</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>45525</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>44901</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>45162</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>45365</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         <v>45019</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>45610</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14936,7 +14936,7 @@
         <v>45568</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>45572</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>45365</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>45610</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         <v>45049</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>45889</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15379,7 +15379,7 @@
         <v>44980</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15452,7 +15452,7 @@
         <v>45890</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15530,7 +15530,7 @@
         <v>45890</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>45020</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15686,7 +15686,7 @@
         <v>45496</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15764,7 +15764,7 @@
         <v>45893</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
         <v>45895</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>45896</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>45215</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>45687</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>45545</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16207,7 +16207,7 @@
         <v>45480</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>45635</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>45141</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>45281</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>45628</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>45468</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16650,7 +16650,7 @@
         <v>45475</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>45251</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>45631</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>44487</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>45610</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17025,7 +17025,7 @@
         <v>45541</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17103,7 +17103,7 @@
         <v>45540</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17181,7 +17181,7 @@
         <v>44913</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         <v>45149</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17332,7 +17332,7 @@
         <v>45162</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>45644</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>45628</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>45160</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17624,7 +17624,7 @@
         <v>45909</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>45474</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>45161</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>44876</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>45246</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17994,7 +17994,7 @@
         <v>45246</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18067,7 +18067,7 @@
         <v>45246</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18140,7 +18140,7 @@
         <v>45458</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18213,7 +18213,7 @@
         <v>45160</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>45915</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>44551</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>45484</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>44894</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>44901</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18656,7 +18656,7 @@
         <v>45357</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>45918</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>45041</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>45302</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>45583</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>45617</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19099,7 +19099,7 @@
         <v>45405</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>45919</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>45005</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>45924</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19396,7 +19396,7 @@
         <v>45642</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>45495</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19547,7 +19547,7 @@
         <v>45926</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>45335</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
         <v>45082</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19771,7 +19771,7 @@
         <v>45712</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>45512</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>45678</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         <v>45030</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20068,7 +20068,7 @@
         <v>45188</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20141,7 +20141,7 @@
         <v>45636</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>45182</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>45929</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20365,7 +20365,7 @@
         <v>45794</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
         <v>45496</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>45553</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>45701</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>45191</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>45404</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>44580</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>45761</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20954,7 +20954,7 @@
         <v>45627</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21027,7 +21027,7 @@
         <v>45800</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>45679</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21173,7 +21173,7 @@
         <v>45800</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>45610</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>44683</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>45548</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>45803</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>45803</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>45625</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>44732</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>45938</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>45601</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>44805</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21991,7 +21991,7 @@
         <v>45687</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>45600</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22137,7 +22137,7 @@
         <v>45184</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22215,7 +22215,7 @@
         <v>45246</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22288,7 +22288,7 @@
         <v>45636</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22361,7 +22361,7 @@
         <v>45687</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22434,7 +22434,7 @@
         <v>45559</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>45708</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         <v>44588</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>44622</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>45782</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22809,7 +22809,7 @@
         <v>45653</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>45664</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>45712</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>45251</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23106,7 +23106,7 @@
         <v>45559</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23179,7 +23179,7 @@
         <v>45607</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>45813</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23325,7 +23325,7 @@
         <v>44699</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>45818</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>45671</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>45659</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>44960</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23690,7 +23690,7 @@
         <v>44960</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>44960</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>45079</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>45565</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>45611</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>45020</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24133,7 +24133,7 @@
         <v>45670</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>44952</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24279,7 +24279,7 @@
         <v>44838</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24352,7 +24352,7 @@
         <v>45446</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24425,7 +24425,7 @@
         <v>44516</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24498,7 +24498,7 @@
         <v>45090</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24571,7 +24571,7 @@
         <v>45700</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24644,7 +24644,7 @@
         <v>45832</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>45831</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>45205</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>45957</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>45958</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25019,7 +25019,7 @@
         <v>45957</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>45959</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25170,7 +25170,7 @@
         <v>45959</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25243,7 +25243,7 @@
         <v>45202</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25316,7 +25316,7 @@
         <v>45474</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25394,7 +25394,7 @@
         <v>45960</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25472,7 +25472,7 @@
         <v>45961</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>45839</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>45965</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>45966</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25774,7 +25774,7 @@
         <v>45965</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25847,7 +25847,7 @@
         <v>45839</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25920,7 +25920,7 @@
         <v>45839</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25993,7 +25993,7 @@
         <v>45839</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26066,7 +26066,7 @@
         <v>45839</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26139,7 +26139,7 @@
         <v>45839</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26212,7 +26212,7 @@
         <v>45715</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26290,7 +26290,7 @@
         <v>45965</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26363,7 +26363,7 @@
         <v>45659</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26436,7 +26436,7 @@
         <v>45965</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26509,7 +26509,7 @@
         <v>45841</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>45667</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>45841</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26733,7 +26733,7 @@
         <v>45661</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26806,7 +26806,7 @@
         <v>45664</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26879,7 +26879,7 @@
         <v>45184</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26952,7 +26952,7 @@
         <v>45635</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27025,7 +27025,7 @@
         <v>45033</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>45708</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27171,7 +27171,7 @@
         <v>45756</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27244,7 +27244,7 @@
         <v>44783</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27317,7 +27317,7 @@
         <v>45974</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27395,7 +27395,7 @@
         <v>45644</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>45463</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27541,7 +27541,7 @@
         <v>45856</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27614,7 +27614,7 @@
         <v>45458</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27687,7 +27687,7 @@
         <v>45856</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27760,7 +27760,7 @@
         <v>45856</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27833,7 +27833,7 @@
         <v>45789</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>45205</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27979,7 +27979,7 @@
         <v>45301</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28052,7 +28052,7 @@
         <v>45692</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28125,7 +28125,7 @@
         <v>45182</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28198,7 +28198,7 @@
         <v>45197</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28276,7 +28276,7 @@
         <v>45701</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>45870</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>45040</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28495,7 +28495,7 @@
         <v>45013</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28568,7 +28568,7 @@
         <v>45176</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28641,7 +28641,7 @@
         <v>45873</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28714,7 +28714,7 @@
         <v>45687</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>45005</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28860,7 +28860,7 @@
         <v>45981</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28933,7 +28933,7 @@
         <v>45981</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29011,7 +29011,7 @@
         <v>45981</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29089,7 +29089,7 @@
         <v>45537</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29167,7 +29167,7 @@
         <v>45636</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         <v>44938</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29313,7 +29313,7 @@
         <v>45261</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29386,7 +29386,7 @@
         <v>46094</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29464,7 +29464,7 @@
         <v>46099</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>46099</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29610,7 +29610,7 @@
         <v>45002</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29683,7 +29683,7 @@
         <v>45468</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>46104</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29829,7 +29829,7 @@
         <v>45537</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>45644</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29980,7 +29980,7 @@
         <v>46105</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30053,7 +30053,7 @@
         <v>45133</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30131,7 +30131,7 @@
         <v>45510</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30209,7 +30209,7 @@
         <v>45622</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30282,7 +30282,7 @@
         <v>45671</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30355,7 +30355,7 @@
         <v>44980</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30433,7 +30433,7 @@
         <v>45987</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30506,7 +30506,7 @@
         <v>45581</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>45548</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>46122</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>44516</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30798,7 +30798,7 @@
         <v>46126</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30871,7 +30871,7 @@
         <v>45996</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30944,7 +30944,7 @@
         <v>46126</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31017,7 +31017,7 @@
         <v>46000</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>45033</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31168,7 +31168,7 @@
         <v>45048</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31241,7 +31241,7 @@
         <v>46126</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31314,7 +31314,7 @@
         <v>46000</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>44936</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31460,7 +31460,7 @@
         <v>46132</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31538,7 +31538,7 @@
         <v>45432</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31611,7 +31611,7 @@
         <v>44811</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31684,7 +31684,7 @@
         <v>46135</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31757,7 +31757,7 @@
         <v>46135</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31830,7 +31830,7 @@
         <v>46135</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31903,7 +31903,7 @@
         <v>45607</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31976,7 +31976,7 @@
         <v>44502</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32049,7 +32049,7 @@
         <v>44580</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32122,7 +32122,7 @@
         <v>46135</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32195,7 +32195,7 @@
         <v>45901</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32273,7 +32273,7 @@
         <v>45734</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>45246</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>45580</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32497,7 +32497,7 @@
         <v>45502</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32570,7 +32570,7 @@
         <v>46139</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32643,7 +32643,7 @@
         <v>45561</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32716,7 +32716,7 @@
         <v>45238</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32789,7 +32789,7 @@
         <v>46140</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>45470</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32940,7 +32940,7 @@
         <v>46037</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33013,7 +33013,7 @@
         <v>45029</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33086,7 +33086,7 @@
         <v>46042</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33159,7 +33159,7 @@
         <v>45145</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33237,7 +33237,7 @@
         <v>45929</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33315,7 +33315,7 @@
         <v>44734</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33388,7 +33388,7 @@
         <v>45826</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33461,7 +33461,7 @@
         <v>45076</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33534,7 +33534,7 @@
         <v>46048</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33607,7 +33607,7 @@
         <v>45146</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>45930</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>45129</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33831,7 +33831,7 @@
         <v>46050</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33904,7 +33904,7 @@
         <v>46050</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33977,7 +33977,7 @@
         <v>46050</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>46058</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34128,7 +34128,7 @@
         <v>46059</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34201,7 +34201,7 @@
         <v>46059</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34274,7 +34274,7 @@
         <v>46063</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34347,7 +34347,7 @@
         <v>46146</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34425,7 +34425,7 @@
         <v>46146</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>46065</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34571,7 +34571,7 @@
         <v>46148</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34644,7 +34644,7 @@
         <v>46065</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34717,7 +34717,7 @@
         <v>46150</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34795,7 +34795,7 @@
         <v>45678</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34873,7 +34873,7 @@
         <v>46153</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34946,7 +34946,7 @@
         <v>46076</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>46153</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35097,7 +35097,7 @@
         <v>46153</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35170,7 +35170,7 @@
         <v>46153</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35248,7 +35248,7 @@
         <v>46083</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35321,7 +35321,7 @@
         <v>46155</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35394,7 +35394,7 @@
         <v>46160</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35472,7 +35472,7 @@
         <v>46160</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35545,7 +35545,7 @@
         <v>46160</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35618,7 +35618,7 @@
         <v>45502</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35691,7 +35691,7 @@
         <v>45580</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35764,7 +35764,7 @@
         <v>45386</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>46171</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35910,7 +35910,7 @@
         <v>46170</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35983,7 +35983,7 @@
         <v>46171</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36056,7 +36056,7 @@
         <v>46176</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36129,7 +36129,7 @@
         <v>46175</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>46177</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36275,7 +36275,7 @@
         <v>45454</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>46113</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36421,7 +36421,7 @@
         <v>46181</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36494,7 +36494,7 @@
         <v>46183</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36567,7 +36567,7 @@
         <v>46185</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36640,7 +36640,7 @@
         <v>46185</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36713,7 +36713,7 @@
         <v>46185</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36791,7 +36791,7 @@
         <v>46188</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36864,7 +36864,7 @@
         <v>46188</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36937,7 +36937,7 @@
         <v>46188</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>45620</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37083,7 +37083,7 @@
         <v>46198</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37156,7 +37156,7 @@
         <v>46202</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>46203</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37302,7 +37302,7 @@
         <v>46204</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37380,7 +37380,7 @@
         <v>46205</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>46205</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37526,7 +37526,7 @@
         <v>46206</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37599,7 +37599,7 @@
         <v>46266</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37672,7 +37672,7 @@
         <v>46266</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37745,7 +37745,7 @@
         <v>46195</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>46225</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>46268</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37964,7 +37964,7 @@
         <v>46225</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38037,7 +38037,7 @@
         <v>46225</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>46269</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38188,7 +38188,7 @@
         <v>46269</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38266,7 +38266,7 @@
         <v>46269</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38344,7 +38344,7 @@
         <v>46268</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38422,7 +38422,7 @@
         <v>46269</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38500,7 +38500,7 @@
         <v>46269</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38578,7 +38578,7 @@
         <v>46273</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38651,7 +38651,7 @@
         <v>46273</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38724,7 +38724,7 @@
         <v>46230</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38797,7 +38797,7 @@
         <v>46276</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38870,7 +38870,7 @@
         <v>46276</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38948,7 +38948,7 @@
         <v>46279</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39021,7 +39021,7 @@
         <v>46279</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39099,7 +39099,7 @@
         <v>46280</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39177,7 +39177,7 @@
         <v>46280</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39255,7 +39255,7 @@
         <v>46279</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39333,7 +39333,7 @@
         <v>46279</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39411,7 +39411,7 @@
         <v>46239</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39484,7 +39484,7 @@
         <v>46282</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39557,7 +39557,7 @@
         <v>46240</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39630,7 +39630,7 @@
         <v>46282</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39708,7 +39708,7 @@
         <v>46239</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>46240</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>46240</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39927,7 +39927,7 @@
         <v>46240</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40000,7 +40000,7 @@
         <v>46239</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40073,7 +40073,7 @@
         <v>46283</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40151,7 +40151,7 @@
         <v>46240</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>46185</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40297,7 +40297,7 @@
         <v>46240</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40375,7 +40375,7 @@
         <v>46240</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40448,7 +40448,7 @@
         <v>46286</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40526,7 +40526,7 @@
         <v>46286</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40604,7 +40604,7 @@
         <v>46288</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40677,7 +40677,7 @@
         <v>46244</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>46288</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40828,7 +40828,7 @@
         <v>46188</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40901,7 +40901,7 @@
         <v>46191</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40979,7 +40979,7 @@
         <v>46196</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41052,7 +41052,7 @@
         <v>46289</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41130,7 +41130,7 @@
         <v>46240</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41208,7 +41208,7 @@
         <v>46289</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41281,7 +41281,7 @@
         <v>46132</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41359,7 +41359,7 @@
         <v>46289</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41437,7 +41437,7 @@
         <v>46291</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41515,7 +41515,7 @@
         <v>46291</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41593,7 +41593,7 @@
         <v>46297</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41671,7 +41671,7 @@
         <v>46254</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41744,7 +41744,7 @@
         <v>46297</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41822,7 +41822,7 @@
         <v>46297</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41900,7 +41900,7 @@
         <v>46297</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41978,7 +41978,7 @@
         <v>46255</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>46255</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42124,7 +42124,7 @@
         <v>46259</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42197,7 +42197,7 @@
         <v>46112</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42270,7 +42270,7 @@
         <v>46302</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42343,7 +42343,7 @@
         <v>46258</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42416,7 +42416,7 @@
         <v>46258</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42489,7 +42489,7 @@
         <v>46261</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42567,7 +42567,7 @@
         <v>46262</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42645,7 +42645,7 @@
         <v>46239</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42718,7 +42718,7 @@
         <v>46261</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42796,7 +42796,7 @@
         <v>46303</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42874,7 +42874,7 @@
         <v>46303</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42947,7 +42947,7 @@
         <v>44707</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43020,7 +43020,7 @@
         <v>44501</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43093,7 +43093,7 @@
         <v>45747</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43171,7 +43171,7 @@
         <v>45762</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43249,7 +43249,7 @@
         <v>46092</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43322,7 +43322,7 @@
         <v>46147</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43395,7 +43395,7 @@
         <v>46149</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43468,7 +43468,7 @@
         <v>46155</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>

--- a/Översikt ROBERTSFORS.xlsx
+++ b/Översikt ROBERTSFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46097</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45701</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44919</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45250</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45944</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>45936</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>45939</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>45792</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>46070</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>46135</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>45796</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>45967</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>45153</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>46050</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>45891</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45915</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>44725</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>45119</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>46037</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>45848</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>44535</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>45560</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>45504</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>45051</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>45177</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>45937</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>46038</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>46050</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>46050</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>46050</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>45182</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>45182</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>46307</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>46265</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>45468</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>44699</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>44559</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>44803</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>44497</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>45210</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>45153</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>45233</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>45856</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>45245</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>45182</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>45510</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>44823</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>45719</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>45146</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>45124</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         <v>45163</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>45630</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>45957</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>46050</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>46050</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>46050</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>45245</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>46198</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>46204</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         <v>45695</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>45712</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>45176</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>46269</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>45827</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>45835</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>45844</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>44312</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>45747</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>45919</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         <v>44784</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>44810</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>44677</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>44880</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>44734</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         <v>44734</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>44645</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>44858</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>44572</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>44497</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         <v>44721</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>44658</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>44612</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         <v>44612</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
         <v>44641</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>44775</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         <v>44575</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>44735</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>44795</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>44612</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>44855</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>44519</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>44571</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         <v>44532</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>44844</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>44612</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>44612</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>44851</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10382,7 +10382,7 @@
         <v>44729</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>44819</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>44662</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>44697</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>44812</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>44827</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>44841</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>44824</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
         <v>44580</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>44641</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>44574</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>44644</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>44817</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>44615</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>44488</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>44789</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>44627</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>44627</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>45246</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>45687</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>45033</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>45079</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>45625</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>45474</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>45537</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12237,7 +12237,7 @@
         <v>45537</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>45048</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>45548</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>45197</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>45622</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>45700</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>45580</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>45253</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>45019</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>45405</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>45184</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>45496</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>45617</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>45484</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13279,7 +13279,7 @@
         <v>45553</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>45572</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>45559</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>45559</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13576,7 +13576,7 @@
         <v>44894</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>45659</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>45461</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13795,7 +13795,7 @@
         <v>44904</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>45468</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>45715</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14014,7 +14014,7 @@
         <v>45446</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14087,7 +14087,7 @@
         <v>44960</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14160,7 +14160,7 @@
         <v>44960</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>44913</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         <v>45070</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>44902</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>44860</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>45197</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>45251</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>45030</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>45033</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14827,7 +14827,7 @@
         <v>45695</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>44805</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14973,7 +14973,7 @@
         <v>45610</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
         <v>45687</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>45202</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>45090</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
         <v>44953</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>45251</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>45149</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>45458</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>45205</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>45581</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>45715</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
         <v>45617</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>45458</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>45635</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>45029</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>44516</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16161,7 +16161,7 @@
         <v>45480</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16234,7 +16234,7 @@
         <v>45281</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>45661</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         <v>45664</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16453,7 +16453,7 @@
         <v>44516</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>45191</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>45512</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>44783</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16745,7 +16745,7 @@
         <v>44838</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16818,7 +16818,7 @@
         <v>45826</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>45162</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>45653</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
         <v>44938</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>45930</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>44945</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17256,7 +17256,7 @@
         <v>44487</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>46139</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         <v>45901</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>45889</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>45929</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
         <v>45890</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>45544</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         <v>45890</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>45895</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17943,7 +17943,7 @@
         <v>45701</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18016,7 +18016,7 @@
         <v>45893</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>44901</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18162,7 +18162,7 @@
         <v>45896</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>45734</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>45561</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>45246</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>46140</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18537,7 +18537,7 @@
         <v>45335</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18610,7 +18610,7 @@
         <v>45671</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18683,7 +18683,7 @@
         <v>45238</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18756,7 +18756,7 @@
         <v>45541</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18834,7 +18834,7 @@
         <v>45146</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18912,7 +18912,7 @@
         <v>45909</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18985,7 +18985,7 @@
         <v>45540</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>45405</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>45915</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19214,7 +19214,7 @@
         <v>45090</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19287,7 +19287,7 @@
         <v>46146</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>45005</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19438,7 +19438,7 @@
         <v>45918</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19516,7 +19516,7 @@
         <v>45919</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>44580</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>45020</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>46146</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>45924</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>46148</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>44502</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20037,7 +20037,7 @@
         <v>45926</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
         <v>45929</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         <v>46153</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20271,7 +20271,7 @@
         <v>46150</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>46153</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         <v>46153</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>46153</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>45938</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>45782</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20719,7 +20719,7 @@
         <v>45251</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>45510</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20875,7 +20875,7 @@
         <v>45246</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20948,7 +20948,7 @@
         <v>45365</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>45957</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>46155</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>45162</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
         <v>45957</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21313,7 +21313,7 @@
         <v>45958</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21391,7 +21391,7 @@
         <v>45959</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21464,7 +21464,7 @@
         <v>45357</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>45712</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>45959</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21688,7 +21688,7 @@
         <v>45960</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>45628</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>45961</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>45587</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>45965</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>45502</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22141,7 +22141,7 @@
         <v>45965</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22214,7 +22214,7 @@
         <v>45965</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22287,7 +22287,7 @@
         <v>45966</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>46160</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22438,7 +22438,7 @@
         <v>45965</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>46160</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22584,7 +22584,7 @@
         <v>45013</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>44973</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>46160</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>45042</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>45679</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>45974</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>45141</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>45664</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23183,7 +23183,7 @@
         <v>45981</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>45580</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>45981</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23412,7 +23412,7 @@
         <v>45981</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>44936</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23558,7 +23558,7 @@
         <v>44734</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>45987</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>45205</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>45076</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>45020</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>45996</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24001,7 +24001,7 @@
         <v>46000</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24074,7 +24074,7 @@
         <v>46171</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>46000</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>46170</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24298,7 +24298,7 @@
         <v>44980</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24376,7 +24376,7 @@
         <v>45002</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24449,7 +24449,7 @@
         <v>45386</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24522,7 +24522,7 @@
         <v>45129</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24595,7 +24595,7 @@
         <v>45182</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24668,7 +24668,7 @@
         <v>45090</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24741,7 +24741,7 @@
         <v>46171</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24814,7 +24814,7 @@
         <v>45404</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24887,7 +24887,7 @@
         <v>45610</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>45302</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         <v>45611</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>45475</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         <v>45160</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>45635</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>45458</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25408,7 +25408,7 @@
         <v>46175</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25481,7 +25481,7 @@
         <v>46176</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25554,7 +25554,7 @@
         <v>46037</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25627,7 +25627,7 @@
         <v>46113</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>45454</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>46042</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25846,7 +25846,7 @@
         <v>45041</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>46177</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25992,7 +25992,7 @@
         <v>45133</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26070,7 +26070,7 @@
         <v>46181</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26143,7 +26143,7 @@
         <v>46048</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26216,7 +26216,7 @@
         <v>46050</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26289,7 +26289,7 @@
         <v>45756</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26362,7 +26362,7 @@
         <v>46050</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26435,7 +26435,7 @@
         <v>45678</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26513,7 +26513,7 @@
         <v>46050</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>45551</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26659,7 +26659,7 @@
         <v>46058</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26737,7 +26737,7 @@
         <v>45268</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         <v>46059</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26883,7 +26883,7 @@
         <v>45307</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>46059</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27029,7 +27029,7 @@
         <v>46063</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>45607</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27175,7 +27175,7 @@
         <v>46065</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27248,7 +27248,7 @@
         <v>46183</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27321,7 +27321,7 @@
         <v>46065</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27394,7 +27394,7 @@
         <v>45470</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27467,7 +27467,7 @@
         <v>46185</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27540,7 +27540,7 @@
         <v>45301</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27613,7 +27613,7 @@
         <v>46185</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27686,7 +27686,7 @@
         <v>45712</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27759,7 +27759,7 @@
         <v>46188</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27832,7 +27832,7 @@
         <v>46188</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27905,7 +27905,7 @@
         <v>46188</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>45678</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28056,7 +28056,7 @@
         <v>45261</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         <v>46185</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28207,7 +28207,7 @@
         <v>45617</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28280,7 +28280,7 @@
         <v>45160</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28353,7 +28353,7 @@
         <v>46076</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28426,7 +28426,7 @@
         <v>46083</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         <v>45176</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28572,7 +28572,7 @@
         <v>45365</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28645,7 +28645,7 @@
         <v>45548</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28718,7 +28718,7 @@
         <v>45568</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
         <v>46094</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28869,7 +28869,7 @@
         <v>45667</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28947,7 +28947,7 @@
         <v>45610</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29025,7 +29025,7 @@
         <v>45620</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29098,7 +29098,7 @@
         <v>44580</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29171,7 +29171,7 @@
         <v>45526</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29249,7 +29249,7 @@
         <v>46099</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29322,7 +29322,7 @@
         <v>46099</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>45432</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>46104</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29541,7 +29541,7 @@
         <v>45636</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29614,7 +29614,7 @@
         <v>45644</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29687,7 +29687,7 @@
         <v>46105</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>45601</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>46198</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29911,7 +29911,7 @@
         <v>44876</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>45463</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30057,7 +30057,7 @@
         <v>46122</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>45029</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30203,7 +30203,7 @@
         <v>46126</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>46126</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30349,7 +30349,7 @@
         <v>46126</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30422,7 +30422,7 @@
         <v>46202</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30495,7 +30495,7 @@
         <v>46204</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>46132</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30651,7 +30651,7 @@
         <v>45565</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30724,7 +30724,7 @@
         <v>46135</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30797,7 +30797,7 @@
         <v>45627</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30870,7 +30870,7 @@
         <v>46135</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30943,7 +30943,7 @@
         <v>45215</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>46135</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31089,7 +31089,7 @@
         <v>46203</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31162,7 +31162,7 @@
         <v>46135</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>45502</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31308,7 +31308,7 @@
         <v>45049</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31381,7 +31381,7 @@
         <v>44901</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>45145</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31532,7 +31532,7 @@
         <v>45600</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31605,7 +31605,7 @@
         <v>46206</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31678,7 +31678,7 @@
         <v>46205</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>46205</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31824,7 +31824,7 @@
         <v>45250</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>45610</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31975,7 +31975,7 @@
         <v>45583</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32048,7 +32048,7 @@
         <v>44571</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32121,7 +32121,7 @@
         <v>44895</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32194,7 +32194,7 @@
         <v>45468</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32267,7 +32267,7 @@
         <v>45545</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32340,7 +32340,7 @@
         <v>45664</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32413,7 +32413,7 @@
         <v>45708</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32486,7 +32486,7 @@
         <v>46195</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32559,7 +32559,7 @@
         <v>45496</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32637,7 +32637,7 @@
         <v>44622</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32715,7 +32715,7 @@
         <v>45082</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32788,7 +32788,7 @@
         <v>46225</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32861,7 +32861,7 @@
         <v>46225</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32934,7 +32934,7 @@
         <v>46225</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33007,7 +33007,7 @@
         <v>45644</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33080,7 +33080,7 @@
         <v>44952</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33153,7 +33153,7 @@
         <v>44980</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>46273</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>46230</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33372,7 +33372,7 @@
         <v>46273</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33445,7 +33445,7 @@
         <v>45708</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33518,7 +33518,7 @@
         <v>45184</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33596,7 +33596,7 @@
         <v>46279</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33669,7 +33669,7 @@
         <v>46279</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33747,7 +33747,7 @@
         <v>46276</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33820,7 +33820,7 @@
         <v>45607</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33893,7 +33893,7 @@
         <v>46279</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33971,7 +33971,7 @@
         <v>46279</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34049,7 +34049,7 @@
         <v>45659</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34122,7 +34122,7 @@
         <v>44980</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34195,7 +34195,7 @@
         <v>46276</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34273,7 +34273,7 @@
         <v>45182</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34346,7 +34346,7 @@
         <v>46280</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34424,7 +34424,7 @@
         <v>45631</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>46280</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34575,7 +34575,7 @@
         <v>46239</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34648,7 +34648,7 @@
         <v>46240</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34721,7 +34721,7 @@
         <v>46240</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>46240</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34867,7 +34867,7 @@
         <v>46239</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>46282</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35018,7 +35018,7 @@
         <v>46239</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35091,7 +35091,7 @@
         <v>46240</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35169,7 +35169,7 @@
         <v>45135</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>46282</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35320,7 +35320,7 @@
         <v>46240</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35393,7 +35393,7 @@
         <v>46283</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35471,7 +35471,7 @@
         <v>46240</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35544,7 +35544,7 @@
         <v>46240</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35617,7 +35617,7 @@
         <v>46286</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>46185</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35768,7 +35768,7 @@
         <v>45636</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35841,7 +35841,7 @@
         <v>45040</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>46286</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35992,7 +35992,7 @@
         <v>46244</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>44683</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36143,7 +36143,7 @@
         <v>45530</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36216,7 +36216,7 @@
         <v>46288</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36289,7 +36289,7 @@
         <v>44960</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36362,7 +36362,7 @@
         <v>44588</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>46289</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36508,7 +36508,7 @@
         <v>46289</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36586,7 +36586,7 @@
         <v>46288</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>46289</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36742,7 +36742,7 @@
         <v>46240</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36820,7 +36820,7 @@
         <v>45659</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36893,7 +36893,7 @@
         <v>46196</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36966,7 +36966,7 @@
         <v>46291</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37044,7 +37044,7 @@
         <v>46188</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37117,7 +37117,7 @@
         <v>45525</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37190,7 +37190,7 @@
         <v>45692</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37263,7 +37263,7 @@
         <v>46291</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37341,7 +37341,7 @@
         <v>46132</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37419,7 +37419,7 @@
         <v>45671</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37492,7 +37492,7 @@
         <v>44551</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>44732</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37638,7 +37638,7 @@
         <v>46191</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37716,7 +37716,7 @@
         <v>44811</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37789,7 +37789,7 @@
         <v>44699</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37862,7 +37862,7 @@
         <v>44901</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37935,7 +37935,7 @@
         <v>45005</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38008,7 +38008,7 @@
         <v>45148</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38086,7 +38086,7 @@
         <v>45670</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38159,7 +38159,7 @@
         <v>46297</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>45687</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38310,7 +38310,7 @@
         <v>46297</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38388,7 +38388,7 @@
         <v>46297</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38466,7 +38466,7 @@
         <v>46297</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>46254</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38617,7 +38617,7 @@
         <v>46255</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38690,7 +38690,7 @@
         <v>46255</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>45701</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38836,7 +38836,7 @@
         <v>46112</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38909,7 +38909,7 @@
         <v>46258</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>45161</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39055,7 +39055,7 @@
         <v>45246</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39128,7 +39128,7 @@
         <v>45246</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>45160</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39274,7 +39274,7 @@
         <v>45644</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39347,7 +39347,7 @@
         <v>45628</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39420,7 +39420,7 @@
         <v>46259</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>45495</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39571,7 +39571,7 @@
         <v>46302</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39644,7 +39644,7 @@
         <v>45642</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39717,7 +39717,7 @@
         <v>45188</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>46303</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39868,7 +39868,7 @@
         <v>46303</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39941,7 +39941,7 @@
         <v>46258</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40014,7 +40014,7 @@
         <v>46262</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40092,7 +40092,7 @@
         <v>46239</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40165,7 +40165,7 @@
         <v>46261</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40243,7 +40243,7 @@
         <v>46261</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40321,7 +40321,7 @@
         <v>45794</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40394,7 +40394,7 @@
         <v>45761</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40467,7 +40467,7 @@
         <v>45800</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40540,7 +40540,7 @@
         <v>45800</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40613,7 +40613,7 @@
         <v>45803</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40686,7 +40686,7 @@
         <v>45803</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40759,7 +40759,7 @@
         <v>46308</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40832,7 +40832,7 @@
         <v>46266</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40905,7 +40905,7 @@
         <v>45687</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>46266</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41051,7 +41051,7 @@
         <v>46308</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41124,7 +41124,7 @@
         <v>45636</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41197,7 +41197,7 @@
         <v>46268</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41270,7 +41270,7 @@
         <v>45813</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41343,7 +41343,7 @@
         <v>46269</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41421,7 +41421,7 @@
         <v>46269</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41499,7 +41499,7 @@
         <v>45818</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41572,7 +41572,7 @@
         <v>46269</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41650,7 +41650,7 @@
         <v>46268</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41728,7 +41728,7 @@
         <v>46269</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41806,7 +41806,7 @@
         <v>46269</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41884,7 +41884,7 @@
         <v>45831</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41957,7 +41957,7 @@
         <v>45832</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42035,7 +42035,7 @@
         <v>45839</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42108,7 +42108,7 @@
         <v>45474</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42186,7 +42186,7 @@
         <v>45839</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42259,7 +42259,7 @@
         <v>45839</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>45839</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42405,7 +42405,7 @@
         <v>45839</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42478,7 +42478,7 @@
         <v>45839</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42551,7 +42551,7 @@
         <v>45841</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42624,7 +42624,7 @@
         <v>45841</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42697,7 +42697,7 @@
         <v>45856</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>45856</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42843,7 +42843,7 @@
         <v>45856</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>45789</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42989,7 +42989,7 @@
         <v>45870</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43062,7 +43062,7 @@
         <v>45873</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43135,7 +43135,7 @@
         <v>44707</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43208,7 +43208,7 @@
         <v>44501</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43281,7 +43281,7 @@
         <v>45747</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43359,7 +43359,7 @@
         <v>45762</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
         <v>46092</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43510,7 +43510,7 @@
         <v>46147</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43583,7 +43583,7 @@
         <v>46149</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43656,7 +43656,7 @@
         <v>46155</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>

--- a/Översikt ROBERTSFORS.xlsx
+++ b/Översikt ROBERTSFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46097</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45701</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44919</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45250</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45944</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>45936</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>45939</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>45792</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>46070</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>46135</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>45796</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>45967</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>45153</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>46050</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>45891</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45915</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>44725</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>45119</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>46037</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>45848</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>44535</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>45560</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>45504</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>45051</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>45177</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>45937</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>46038</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>46050</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>46050</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>46050</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>45182</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>45182</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>46307</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>46265</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>45468</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>44699</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>44559</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>44803</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>44497</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>45210</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>45153</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>45233</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>45856</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>45245</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>45182</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>45510</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>44823</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>45719</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>45146</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>45124</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
         <v>45163</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>45630</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>45957</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>46050</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>46050</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>46050</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>45245</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>46198</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>46204</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         <v>45695</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>45712</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>45176</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>46269</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>45827</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>45835</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>45844</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>44312</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>45747</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>45919</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         <v>44784</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>44810</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>44677</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>44880</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>44734</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         <v>44734</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>44645</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>44858</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>44572</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>44497</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         <v>44721</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>44658</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>44612</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         <v>44612</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
         <v>44641</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>44775</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         <v>44575</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>44735</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>44795</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>44612</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>44855</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>44519</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>44571</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         <v>44532</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>44844</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>44612</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>44612</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>44851</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10382,7 +10382,7 @@
         <v>44729</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>44819</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>44662</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>44697</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>44812</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>44827</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>44841</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>44824</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
         <v>44580</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>44641</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>44574</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>44644</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>44817</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>44615</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>44488</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>44789</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>44627</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>44627</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>45246</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>45687</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>45033</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>45079</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>45625</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>45474</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>45537</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12237,7 +12237,7 @@
         <v>45537</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>45048</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>45548</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>45197</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>45622</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>45700</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>45580</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>45253</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>45019</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>45405</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>45184</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>45496</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>45617</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>45484</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13279,7 +13279,7 @@
         <v>45553</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>45572</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>45559</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>45559</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13576,7 +13576,7 @@
         <v>44894</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>45659</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>45461</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13795,7 +13795,7 @@
         <v>44904</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>45468</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>45715</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14014,7 +14014,7 @@
         <v>45446</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14087,7 +14087,7 @@
         <v>44960</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14160,7 +14160,7 @@
         <v>44960</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>44913</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         <v>45070</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>44902</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>44860</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>45197</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>45251</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>45030</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>45033</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14827,7 +14827,7 @@
         <v>45695</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>44805</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14973,7 +14973,7 @@
         <v>45610</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
         <v>45687</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>45202</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>45090</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
         <v>44953</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>45251</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>45149</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>45458</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>45205</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>45581</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>45715</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
         <v>45617</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>45458</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>45635</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>45029</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>44516</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16161,7 +16161,7 @@
         <v>45480</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16234,7 +16234,7 @@
         <v>45281</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>45661</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         <v>45664</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16453,7 +16453,7 @@
         <v>44516</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>45191</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>45512</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>44783</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16745,7 +16745,7 @@
         <v>44838</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16818,7 +16818,7 @@
         <v>45826</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>45162</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>45653</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
         <v>44938</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>45930</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>44945</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17256,7 +17256,7 @@
         <v>44487</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>46139</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         <v>45901</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>45889</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>45929</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
         <v>45890</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>45544</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         <v>45890</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>45895</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17943,7 +17943,7 @@
         <v>45701</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18016,7 +18016,7 @@
         <v>45893</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>44901</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18162,7 +18162,7 @@
         <v>45896</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>45734</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>45561</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>45246</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>46140</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18537,7 +18537,7 @@
         <v>45335</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18610,7 +18610,7 @@
         <v>45671</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18683,7 +18683,7 @@
         <v>45238</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18756,7 +18756,7 @@
         <v>45541</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18834,7 +18834,7 @@
         <v>45146</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18912,7 +18912,7 @@
         <v>45909</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18985,7 +18985,7 @@
         <v>45540</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>45405</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>45915</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19214,7 +19214,7 @@
         <v>45090</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19287,7 +19287,7 @@
         <v>46146</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>45005</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19438,7 +19438,7 @@
         <v>45918</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19516,7 +19516,7 @@
         <v>45919</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>44580</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>45020</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>46146</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>45924</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>46148</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>44502</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20037,7 +20037,7 @@
         <v>45926</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
         <v>45929</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         <v>46153</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20271,7 +20271,7 @@
         <v>46150</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>46153</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         <v>46153</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>46153</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>45938</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>45782</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20719,7 +20719,7 @@
         <v>45251</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>45510</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20875,7 +20875,7 @@
         <v>45246</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20948,7 +20948,7 @@
         <v>45365</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>45957</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>46155</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>45162</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
         <v>45957</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21313,7 +21313,7 @@
         <v>45958</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21391,7 +21391,7 @@
         <v>45959</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21464,7 +21464,7 @@
         <v>45357</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>45712</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>45959</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21688,7 +21688,7 @@
         <v>45960</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>45628</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>45961</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>45587</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>45965</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>45502</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22141,7 +22141,7 @@
         <v>45965</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22214,7 +22214,7 @@
         <v>45965</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22287,7 +22287,7 @@
         <v>45966</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>46160</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22438,7 +22438,7 @@
         <v>45965</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>46160</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22584,7 +22584,7 @@
         <v>45013</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>44973</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>46160</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>45042</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>45679</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>45974</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>45141</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>45664</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23183,7 +23183,7 @@
         <v>45981</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>45580</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>45981</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23412,7 +23412,7 @@
         <v>45981</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>44936</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23558,7 +23558,7 @@
         <v>44734</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>45987</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>45205</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>45076</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>45020</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>45996</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24001,7 +24001,7 @@
         <v>46000</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24074,7 +24074,7 @@
         <v>46171</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>46000</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>46170</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24298,7 +24298,7 @@
         <v>44980</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24376,7 +24376,7 @@
         <v>45002</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24449,7 +24449,7 @@
         <v>45386</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24522,7 +24522,7 @@
         <v>45129</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24595,7 +24595,7 @@
         <v>45182</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24668,7 +24668,7 @@
         <v>45090</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24741,7 +24741,7 @@
         <v>46171</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24814,7 +24814,7 @@
         <v>45404</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24887,7 +24887,7 @@
         <v>45610</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>45302</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         <v>45611</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>45475</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         <v>45160</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>45635</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>45458</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25408,7 +25408,7 @@
         <v>46175</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25481,7 +25481,7 @@
         <v>46176</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25554,7 +25554,7 @@
         <v>46037</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25627,7 +25627,7 @@
         <v>46113</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>45454</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>46042</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25846,7 +25846,7 @@
         <v>45041</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>46177</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25992,7 +25992,7 @@
         <v>45133</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26070,7 +26070,7 @@
         <v>46181</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26143,7 +26143,7 @@
         <v>46048</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26216,7 +26216,7 @@
         <v>46050</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26289,7 +26289,7 @@
         <v>45756</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26362,7 +26362,7 @@
         <v>46050</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26435,7 +26435,7 @@
         <v>45678</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26513,7 +26513,7 @@
         <v>46050</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>45551</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26659,7 +26659,7 @@
         <v>46058</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26737,7 +26737,7 @@
         <v>45268</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         <v>46059</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26883,7 +26883,7 @@
         <v>45307</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>46059</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27029,7 +27029,7 @@
         <v>46063</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>45607</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27175,7 +27175,7 @@
         <v>46065</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27248,7 +27248,7 @@
         <v>46183</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27321,7 +27321,7 @@
         <v>46065</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27394,7 +27394,7 @@
         <v>45470</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27467,7 +27467,7 @@
         <v>46185</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27540,7 +27540,7 @@
         <v>45301</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27613,7 +27613,7 @@
         <v>46185</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27686,7 +27686,7 @@
         <v>45712</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27759,7 +27759,7 @@
         <v>46188</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27832,7 +27832,7 @@
         <v>46188</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27905,7 +27905,7 @@
         <v>46188</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>45678</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28056,7 +28056,7 @@
         <v>45261</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         <v>46185</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28207,7 +28207,7 @@
         <v>45617</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28280,7 +28280,7 @@
         <v>45160</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28353,7 +28353,7 @@
         <v>46076</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28426,7 +28426,7 @@
         <v>46083</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         <v>45176</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28572,7 +28572,7 @@
         <v>45365</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28645,7 +28645,7 @@
         <v>45548</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28718,7 +28718,7 @@
         <v>45568</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
         <v>46094</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28869,7 +28869,7 @@
         <v>45667</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28947,7 +28947,7 @@
         <v>45610</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29025,7 +29025,7 @@
         <v>45620</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29098,7 +29098,7 @@
         <v>44580</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29171,7 +29171,7 @@
         <v>45526</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29249,7 +29249,7 @@
         <v>46099</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29322,7 +29322,7 @@
         <v>46099</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>45432</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>46104</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29541,7 +29541,7 @@
         <v>45636</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29614,7 +29614,7 @@
         <v>45644</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29687,7 +29687,7 @@
         <v>46105</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>45601</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>46198</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29911,7 +29911,7 @@
         <v>44876</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>45463</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30057,7 +30057,7 @@
         <v>46122</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>45029</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30203,7 +30203,7 @@
         <v>46126</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>46126</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30349,7 +30349,7 @@
         <v>46126</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30422,7 +30422,7 @@
         <v>46202</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30495,7 +30495,7 @@
         <v>46204</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>46132</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30651,7 +30651,7 @@
         <v>45565</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30724,7 +30724,7 @@
         <v>46135</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30797,7 +30797,7 @@
         <v>45627</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30870,7 +30870,7 @@
         <v>46135</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30943,7 +30943,7 @@
         <v>45215</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>46135</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31089,7 +31089,7 @@
         <v>46203</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31162,7 +31162,7 @@
         <v>46135</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>45502</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31308,7 +31308,7 @@
         <v>45049</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31381,7 +31381,7 @@
         <v>44901</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>45145</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31532,7 +31532,7 @@
         <v>45600</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31605,7 +31605,7 @@
         <v>46206</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31678,7 +31678,7 @@
         <v>46205</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>46205</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31824,7 +31824,7 @@
         <v>45250</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>45610</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31975,7 +31975,7 @@
         <v>45583</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32048,7 +32048,7 @@
         <v>44571</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32121,7 +32121,7 @@
         <v>44895</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32194,7 +32194,7 @@
         <v>45468</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32267,7 +32267,7 @@
         <v>45545</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32340,7 +32340,7 @@
         <v>45664</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32413,7 +32413,7 @@
         <v>45708</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32486,7 +32486,7 @@
         <v>46195</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32559,7 +32559,7 @@
         <v>45496</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32637,7 +32637,7 @@
         <v>44622</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32715,7 +32715,7 @@
         <v>45082</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32788,7 +32788,7 @@
         <v>46225</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32861,7 +32861,7 @@
         <v>46225</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32934,7 +32934,7 @@
         <v>46225</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33007,7 +33007,7 @@
         <v>45644</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33080,7 +33080,7 @@
         <v>44952</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33153,7 +33153,7 @@
         <v>44980</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>46273</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>46230</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33372,7 +33372,7 @@
         <v>46273</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33445,7 +33445,7 @@
         <v>45708</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33518,7 +33518,7 @@
         <v>45184</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33596,7 +33596,7 @@
         <v>46279</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33669,7 +33669,7 @@
         <v>46279</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33747,7 +33747,7 @@
         <v>46276</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33820,7 +33820,7 @@
         <v>45607</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33893,7 +33893,7 @@
         <v>46279</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33971,7 +33971,7 @@
         <v>46279</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34049,7 +34049,7 @@
         <v>45659</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34122,7 +34122,7 @@
         <v>44980</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34195,7 +34195,7 @@
         <v>46276</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34273,7 +34273,7 @@
         <v>45182</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34346,7 +34346,7 @@
         <v>46280</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34424,7 +34424,7 @@
         <v>45631</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>46280</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34575,7 +34575,7 @@
         <v>46239</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34648,7 +34648,7 @@
         <v>46240</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34721,7 +34721,7 @@
         <v>46240</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>46240</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34867,7 +34867,7 @@
         <v>46239</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>46282</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35018,7 +35018,7 @@
         <v>46239</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35091,7 +35091,7 @@
         <v>46240</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35169,7 +35169,7 @@
         <v>45135</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>46282</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35320,7 +35320,7 @@
         <v>46240</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35393,7 +35393,7 @@
         <v>46283</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35471,7 +35471,7 @@
         <v>46240</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35544,7 +35544,7 @@
         <v>46240</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35617,7 +35617,7 @@
         <v>46286</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>46185</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35768,7 +35768,7 @@
         <v>45636</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35841,7 +35841,7 @@
         <v>45040</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>46286</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35992,7 +35992,7 @@
         <v>46244</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>44683</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36143,7 +36143,7 @@
         <v>45530</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36216,7 +36216,7 @@
         <v>46288</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36289,7 +36289,7 @@
         <v>44960</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36362,7 +36362,7 @@
         <v>44588</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>46289</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36508,7 +36508,7 @@
         <v>46289</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36586,7 +36586,7 @@
         <v>46288</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>46289</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36742,7 +36742,7 @@
         <v>46240</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36820,7 +36820,7 @@
         <v>45659</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36893,7 +36893,7 @@
         <v>46196</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36966,7 +36966,7 @@
         <v>46291</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37044,7 +37044,7 @@
         <v>46188</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37117,7 +37117,7 @@
         <v>45525</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37190,7 +37190,7 @@
         <v>45692</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37263,7 +37263,7 @@
         <v>46291</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37341,7 +37341,7 @@
         <v>46132</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37419,7 +37419,7 @@
         <v>45671</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37492,7 +37492,7 @@
         <v>44551</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>44732</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37638,7 +37638,7 @@
         <v>46191</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37716,7 +37716,7 @@
         <v>44811</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37789,7 +37789,7 @@
         <v>44699</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37862,7 +37862,7 @@
         <v>44901</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37935,7 +37935,7 @@
         <v>45005</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38008,7 +38008,7 @@
         <v>45148</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38086,7 +38086,7 @@
         <v>45670</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38159,7 +38159,7 @@
         <v>46297</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>45687</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38310,7 +38310,7 @@
         <v>46297</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38388,7 +38388,7 @@
         <v>46297</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38466,7 +38466,7 @@
         <v>46297</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>46254</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38617,7 +38617,7 @@
         <v>46255</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38690,7 +38690,7 @@
         <v>46255</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>45701</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38836,7 +38836,7 @@
         <v>46112</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38909,7 +38909,7 @@
         <v>46258</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>45161</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39055,7 +39055,7 @@
         <v>45246</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39128,7 +39128,7 @@
         <v>45246</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>45160</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39274,7 +39274,7 @@
         <v>45644</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39347,7 +39347,7 @@
         <v>45628</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39420,7 +39420,7 @@
         <v>46259</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>45495</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39571,7 +39571,7 @@
         <v>46302</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39644,7 +39644,7 @@
         <v>45642</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39717,7 +39717,7 @@
         <v>45188</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>46303</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39868,7 +39868,7 @@
         <v>46303</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39941,7 +39941,7 @@
         <v>46258</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40014,7 +40014,7 @@
         <v>46262</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40092,7 +40092,7 @@
         <v>46239</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40165,7 +40165,7 @@
         <v>46261</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40243,7 +40243,7 @@
         <v>46261</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40321,7 +40321,7 @@
         <v>45794</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40394,7 +40394,7 @@
         <v>45761</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40467,7 +40467,7 @@
         <v>45800</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40540,7 +40540,7 @@
         <v>45800</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40613,7 +40613,7 @@
         <v>45803</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40686,7 +40686,7 @@
         <v>45803</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40759,7 +40759,7 @@
         <v>46308</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40832,7 +40832,7 @@
         <v>46266</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40905,7 +40905,7 @@
         <v>45687</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>46266</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41051,7 +41051,7 @@
         <v>46308</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41124,7 +41124,7 @@
         <v>45636</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41197,7 +41197,7 @@
         <v>46268</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41270,7 +41270,7 @@
         <v>45813</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41343,7 +41343,7 @@
         <v>46269</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41421,7 +41421,7 @@
         <v>46269</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41499,7 +41499,7 @@
         <v>45818</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41572,7 +41572,7 @@
         <v>46269</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41650,7 +41650,7 @@
         <v>46268</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41728,7 +41728,7 @@
         <v>46269</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41806,7 +41806,7 @@
         <v>46269</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41884,7 +41884,7 @@
         <v>45831</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41957,7 +41957,7 @@
         <v>45832</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42035,7 +42035,7 @@
         <v>45839</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42108,7 +42108,7 @@
         <v>45474</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42186,7 +42186,7 @@
         <v>45839</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42259,7 +42259,7 @@
         <v>45839</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>45839</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42405,7 +42405,7 @@
         <v>45839</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42478,7 +42478,7 @@
         <v>45839</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42551,7 +42551,7 @@
         <v>45841</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42624,7 +42624,7 @@
         <v>45841</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42697,7 +42697,7 @@
         <v>45856</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>45856</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42843,7 +42843,7 @@
         <v>45856</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>45789</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42989,7 +42989,7 @@
         <v>45870</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43062,7 +43062,7 @@
         <v>45873</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43135,7 +43135,7 @@
         <v>44707</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43208,7 +43208,7 @@
         <v>44501</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43281,7 +43281,7 @@
         <v>45747</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43359,7 +43359,7 @@
         <v>45762</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
         <v>46092</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43510,7 +43510,7 @@
         <v>46147</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43583,7 +43583,7 @@
         <v>46149</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43656,7 +43656,7 @@
         <v>46155</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>

--- a/Översikt ROBERTSFORS.xlsx
+++ b/Översikt ROBERTSFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46097</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45701</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44919</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45250</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45944</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>45936</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>45792</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>45939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>46070</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>46135</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>45796</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>45967</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>45153</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>46050</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>45891</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45915</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>44725</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>45848</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>46037</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>45119</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>44535</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>45560</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>45937</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>46038</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>46050</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>46050</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>46050</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>45468</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>46307</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>46265</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>45051</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>45182</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>45504</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>45177</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>45182</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>44699</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>44559</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>44803</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>44497</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>45210</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>45695</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>45957</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>45510</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>44823</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>45233</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>46198</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>46204</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>46050</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>46050</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>46050</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>45827</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>45835</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         <v>45844</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>45182</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>45856</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>46269</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>45146</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
         <v>45719</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>45245</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         <v>45163</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>45176</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>45124</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>45153</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>45630</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>45712</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7883,7 +7883,7 @@
         <v>45245</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>44312</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>45747</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>45919</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         <v>44784</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>44810</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>44677</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>44880</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>44734</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         <v>44734</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>44858</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>44645</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>44572</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>44497</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         <v>44721</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>44658</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>44612</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         <v>44612</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
         <v>44641</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>44775</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         <v>44575</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>44735</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>44795</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>44855</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>44612</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>44519</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>44571</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         <v>44532</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>44844</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>44612</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>44612</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>44851</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10382,7 +10382,7 @@
         <v>44729</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>44819</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>44662</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>44697</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>44812</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>44827</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>44841</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>44824</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
         <v>44580</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>44574</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>44641</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>44644</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>44817</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>44615</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>44627</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>44627</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>44789</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>45042</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>45715</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>45268</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>45889</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>45890</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         <v>45890</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
         <v>45893</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>45607</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12237,7 +12237,7 @@
         <v>45895</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>45896</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>44502</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>44580</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>45029</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>45541</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>46160</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>45540</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>45909</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>45502</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>45580</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>45915</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>45918</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>45919</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>45470</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>45029</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>45924</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>45926</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         <v>45580</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13664,7 +13664,7 @@
         <v>44734</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>45386</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>46171</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>45929</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13961,7 +13961,7 @@
         <v>46170</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>46171</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>45076</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>45129</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14253,7 +14253,7 @@
         <v>46176</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>45938</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>46175</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14472,7 +14472,7 @@
         <v>45160</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>45250</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>46177</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>45782</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>45253</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>45454</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>46113</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>44945</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>45526</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>45090</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>46181</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>45461</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>46183</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>44904</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>46185</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>46185</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>45957</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>45958</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>45957</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>45959</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>46185</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>45959</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>46188</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16176,7 +16176,7 @@
         <v>45960</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>45961</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16332,7 +16332,7 @@
         <v>45965</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>45966</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16483,7 +16483,7 @@
         <v>45965</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16556,7 +16556,7 @@
         <v>46188</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16629,7 +16629,7 @@
         <v>46188</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>45965</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16775,7 +16775,7 @@
         <v>45965</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         <v>45530</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>45620</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16994,7 +16994,7 @@
         <v>45307</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17067,7 +17067,7 @@
         <v>45197</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         <v>45664</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>45659</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>45974</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17369,7 +17369,7 @@
         <v>45251</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>45148</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17525,7 +17525,7 @@
         <v>46198</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17598,7 +17598,7 @@
         <v>46202</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17671,7 +17671,7 @@
         <v>45525</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17744,7 +17744,7 @@
         <v>46203</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17817,7 +17817,7 @@
         <v>45981</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>45981</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17968,7 +17968,7 @@
         <v>45981</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18046,7 +18046,7 @@
         <v>45162</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18119,7 +18119,7 @@
         <v>46204</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18197,7 +18197,7 @@
         <v>45365</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>46205</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>44902</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18416,7 +18416,7 @@
         <v>46205</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18489,7 +18489,7 @@
         <v>45365</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18562,7 +18562,7 @@
         <v>45610</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>44980</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18713,7 +18713,7 @@
         <v>46206</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18786,7 +18786,7 @@
         <v>45987</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>45215</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18932,7 +18932,7 @@
         <v>45687</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>45545</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>44860</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>45551</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19224,7 +19224,7 @@
         <v>45635</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19297,7 +19297,7 @@
         <v>45628</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>45251</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19443,7 +19443,7 @@
         <v>45996</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19516,7 +19516,7 @@
         <v>46000</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>45458</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>45644</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>45628</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>45160</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19886,7 +19886,7 @@
         <v>46195</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>46000</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>45161</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>45246</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>46225</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20251,7 +20251,7 @@
         <v>45246</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20324,7 +20324,7 @@
         <v>46225</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
         <v>46225</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20470,7 +20470,7 @@
         <v>46230</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20543,7 +20543,7 @@
         <v>46279</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20616,7 +20616,7 @@
         <v>46279</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20694,7 +20694,7 @@
         <v>46280</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>46280</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>46279</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20928,7 +20928,7 @@
         <v>46279</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         <v>46239</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         <v>45642</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21152,7 +21152,7 @@
         <v>46282</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21225,7 +21225,7 @@
         <v>46240</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>46282</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>46239</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21449,7 +21449,7 @@
         <v>45495</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>46240</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>45544</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>46240</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>46240</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21824,7 +21824,7 @@
         <v>46239</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21897,7 +21897,7 @@
         <v>46283</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>46240</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>46185</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>45188</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22194,7 +22194,7 @@
         <v>46240</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>46240</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>44973</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22418,7 +22418,7 @@
         <v>46286</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22496,7 +22496,7 @@
         <v>46286</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>46037</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22647,7 +22647,7 @@
         <v>45794</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>46042</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22793,7 +22793,7 @@
         <v>46288</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22866,7 +22866,7 @@
         <v>46244</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>46048</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23012,7 +23012,7 @@
         <v>45761</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>45800</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>46288</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23236,7 +23236,7 @@
         <v>46050</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23309,7 +23309,7 @@
         <v>45800</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23382,7 +23382,7 @@
         <v>46188</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23455,7 +23455,7 @@
         <v>46050</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>46050</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
         <v>46191</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>46196</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23752,7 +23752,7 @@
         <v>45803</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>45803</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>46289</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23976,7 +23976,7 @@
         <v>46240</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
         <v>46289</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>46132</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24205,7 +24205,7 @@
         <v>45687</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         <v>46289</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24356,7 +24356,7 @@
         <v>46058</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24434,7 +24434,7 @@
         <v>46059</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>46059</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24580,7 +24580,7 @@
         <v>45636</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>46291</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
         <v>46063</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>45813</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>46065</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>45818</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>46065</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>46291</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25174,7 +25174,7 @@
         <v>45678</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>46076</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>46083</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25398,7 +25398,7 @@
         <v>45832</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25476,7 +25476,7 @@
         <v>45831</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25549,7 +25549,7 @@
         <v>45474</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25627,7 +25627,7 @@
         <v>45839</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>45839</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>45839</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25846,7 +25846,7 @@
         <v>45839</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>46297</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25997,7 +25997,7 @@
         <v>45839</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26070,7 +26070,7 @@
         <v>45839</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26143,7 +26143,7 @@
         <v>46254</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26216,7 +26216,7 @@
         <v>46297</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>45568</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26367,7 +26367,7 @@
         <v>46094</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>45841</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26518,7 +26518,7 @@
         <v>46297</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26596,7 +26596,7 @@
         <v>45841</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>46099</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26742,7 +26742,7 @@
         <v>46099</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>45496</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>46297</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26971,7 +26971,7 @@
         <v>46255</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>46255</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27117,7 +27117,7 @@
         <v>46104</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>46259</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>46112</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>46302</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27409,7 +27409,7 @@
         <v>46105</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27482,7 +27482,7 @@
         <v>46258</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         <v>45856</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         <v>45856</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>45856</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27774,7 +27774,7 @@
         <v>46258</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>45789</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27920,7 +27920,7 @@
         <v>46261</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>45870</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28071,7 +28071,7 @@
         <v>46261</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>46122</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28222,7 +28222,7 @@
         <v>46303</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28300,7 +28300,7 @@
         <v>46303</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28373,7 +28373,7 @@
         <v>46126</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28446,7 +28446,7 @@
         <v>45873</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28519,7 +28519,7 @@
         <v>46126</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28592,7 +28592,7 @@
         <v>46126</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>45631</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28738,7 +28738,7 @@
         <v>46132</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28816,7 +28816,7 @@
         <v>46262</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28894,7 +28894,7 @@
         <v>44913</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>45162</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>44876</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29113,7 +29113,7 @@
         <v>46239</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>46135</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29259,7 +29259,7 @@
         <v>45160</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29332,7 +29332,7 @@
         <v>46135</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29405,7 +29405,7 @@
         <v>46308</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29478,7 +29478,7 @@
         <v>46135</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29551,7 +29551,7 @@
         <v>44894</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29624,7 +29624,7 @@
         <v>44901</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29697,7 +29697,7 @@
         <v>45357</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29770,7 +29770,7 @@
         <v>46135</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29843,7 +29843,7 @@
         <v>46308</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29916,7 +29916,7 @@
         <v>46266</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>46266</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30062,7 +30062,7 @@
         <v>45901</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30140,7 +30140,7 @@
         <v>45617</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30213,7 +30213,7 @@
         <v>45734</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30286,7 +30286,7 @@
         <v>46268</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>46269</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30442,7 +30442,7 @@
         <v>45246</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30515,7 +30515,7 @@
         <v>46269</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30593,7 +30593,7 @@
         <v>46314</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30666,7 +30666,7 @@
         <v>46314</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30739,7 +30739,7 @@
         <v>45502</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30812,7 +30812,7 @@
         <v>46139</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         <v>46314</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30963,7 +30963,7 @@
         <v>45561</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31036,7 +31036,7 @@
         <v>46314</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31114,7 +31114,7 @@
         <v>45238</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31187,7 +31187,7 @@
         <v>46268</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>46269</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31338,7 +31338,7 @@
         <v>46269</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31416,7 +31416,7 @@
         <v>46314</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>46314</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31572,7 +31572,7 @@
         <v>46269</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31650,7 +31650,7 @@
         <v>46140</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>45145</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31806,7 +31806,7 @@
         <v>45030</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31879,7 +31879,7 @@
         <v>45929</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31957,7 +31957,7 @@
         <v>45636</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>46273</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>45826</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32176,7 +32176,7 @@
         <v>46315</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>46273</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32322,7 +32322,7 @@
         <v>46315</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32400,7 +32400,7 @@
         <v>46315</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32478,7 +32478,7 @@
         <v>45146</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32556,7 +32556,7 @@
         <v>45496</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32634,7 +32634,7 @@
         <v>45930</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>45404</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32780,7 +32780,7 @@
         <v>46276</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>46276</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32931,7 +32931,7 @@
         <v>46317</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33004,7 +33004,7 @@
         <v>46317</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33082,7 +33082,7 @@
         <v>45627</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33155,7 +33155,7 @@
         <v>45679</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33228,7 +33228,7 @@
         <v>46146</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33306,7 +33306,7 @@
         <v>45548</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33379,7 +33379,7 @@
         <v>46146</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>46148</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33525,7 +33525,7 @@
         <v>44732</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>46150</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33676,7 +33676,7 @@
         <v>45600</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>46153</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33822,7 +33822,7 @@
         <v>46153</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33900,7 +33900,7 @@
         <v>45184</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33978,7 +33978,7 @@
         <v>45246</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34051,7 +34051,7 @@
         <v>46153</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34124,7 +34124,7 @@
         <v>45559</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34202,7 +34202,7 @@
         <v>46153</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34280,7 +34280,7 @@
         <v>46155</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34353,7 +34353,7 @@
         <v>45712</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34426,7 +34426,7 @@
         <v>45251</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34504,7 +34504,7 @@
         <v>45559</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>45607</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34650,7 +34650,7 @@
         <v>46160</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34728,7 +34728,7 @@
         <v>45671</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34801,7 +34801,7 @@
         <v>46160</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34874,7 +34874,7 @@
         <v>44960</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34947,7 +34947,7 @@
         <v>44960</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35020,7 +35020,7 @@
         <v>44960</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35093,7 +35093,7 @@
         <v>45079</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35166,7 +35166,7 @@
         <v>45565</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35239,7 +35239,7 @@
         <v>45020</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35317,7 +35317,7 @@
         <v>44952</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35390,7 +35390,7 @@
         <v>44516</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35463,7 +35463,7 @@
         <v>45090</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35536,7 +35536,7 @@
         <v>45205</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>45715</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35687,7 +35687,7 @@
         <v>45659</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35760,7 +35760,7 @@
         <v>45667</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35838,7 +35838,7 @@
         <v>45661</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35911,7 +35911,7 @@
         <v>45664</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35984,7 +35984,7 @@
         <v>45184</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36057,7 +36057,7 @@
         <v>45635</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36130,7 +36130,7 @@
         <v>45033</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36203,7 +36203,7 @@
         <v>45644</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36276,7 +36276,7 @@
         <v>45458</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>45205</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36422,7 +36422,7 @@
         <v>45692</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36495,7 +36495,7 @@
         <v>45182</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36568,7 +36568,7 @@
         <v>45197</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36646,7 +36646,7 @@
         <v>45701</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36719,7 +36719,7 @@
         <v>45040</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36792,7 +36792,7 @@
         <v>45176</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36865,7 +36865,7 @@
         <v>45687</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>45005</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37011,7 +37011,7 @@
         <v>45636</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37084,7 +37084,7 @@
         <v>45002</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>45537</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37235,7 +37235,7 @@
         <v>45133</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37313,7 +37313,7 @@
         <v>45070</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37386,7 +37386,7 @@
         <v>45090</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37459,7 +37459,7 @@
         <v>44901</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37532,7 +37532,7 @@
         <v>44895</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37605,7 +37605,7 @@
         <v>45695</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37678,7 +37678,7 @@
         <v>44980</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37751,7 +37751,7 @@
         <v>45135</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37829,7 +37829,7 @@
         <v>45617</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37902,7 +37902,7 @@
         <v>45617</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37980,7 +37980,7 @@
         <v>44953</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>44571</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38126,7 +38126,7 @@
         <v>45587</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38204,7 +38204,7 @@
         <v>45405</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38277,7 +38277,7 @@
         <v>44901</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38350,7 +38350,7 @@
         <v>45019</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38423,7 +38423,7 @@
         <v>45610</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38501,7 +38501,7 @@
         <v>45572</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38574,7 +38574,7 @@
         <v>45049</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>45020</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38725,7 +38725,7 @@
         <v>45480</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38798,7 +38798,7 @@
         <v>45141</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38876,7 +38876,7 @@
         <v>45281</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38949,7 +38949,7 @@
         <v>45468</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39022,7 +39022,7 @@
         <v>45475</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39095,7 +39095,7 @@
         <v>45610</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>45149</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39251,7 +39251,7 @@
         <v>45474</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>45246</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39402,7 +39402,7 @@
         <v>45458</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39475,7 +39475,7 @@
         <v>44551</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39548,7 +39548,7 @@
         <v>45484</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39621,7 +39621,7 @@
         <v>45041</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>45302</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39767,7 +39767,7 @@
         <v>45583</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39840,7 +39840,7 @@
         <v>45405</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39913,7 +39913,7 @@
         <v>45005</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39986,7 +39986,7 @@
         <v>45335</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40059,7 +40059,7 @@
         <v>45082</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40132,7 +40132,7 @@
         <v>45712</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40205,7 +40205,7 @@
         <v>45512</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>45678</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>45182</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>45553</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40502,7 +40502,7 @@
         <v>45701</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40575,7 +40575,7 @@
         <v>45191</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40648,7 +40648,7 @@
         <v>44580</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40721,7 +40721,7 @@
         <v>45610</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40799,7 +40799,7 @@
         <v>44683</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40877,7 +40877,7 @@
         <v>45625</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40950,7 +40950,7 @@
         <v>45601</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41028,7 +41028,7 @@
         <v>44805</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41101,7 +41101,7 @@
         <v>45687</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41174,7 +41174,7 @@
         <v>45708</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41247,7 +41247,7 @@
         <v>44588</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41320,7 +41320,7 @@
         <v>44622</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41398,7 +41398,7 @@
         <v>45653</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41471,7 +41471,7 @@
         <v>45664</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41544,7 +41544,7 @@
         <v>44699</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41617,7 +41617,7 @@
         <v>45659</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41690,7 +41690,7 @@
         <v>45611</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>45670</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41836,7 +41836,7 @@
         <v>44838</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41909,7 +41909,7 @@
         <v>45446</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41982,7 +41982,7 @@
         <v>45700</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>45202</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42128,7 +42128,7 @@
         <v>45708</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>45756</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>44783</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42347,7 +42347,7 @@
         <v>45463</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42420,7 +42420,7 @@
         <v>45301</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42493,7 +42493,7 @@
         <v>45013</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>45537</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42644,7 +42644,7 @@
         <v>44938</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42717,7 +42717,7 @@
         <v>45261</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42790,7 +42790,7 @@
         <v>45468</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42863,7 +42863,7 @@
         <v>45644</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42936,7 +42936,7 @@
         <v>45510</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43014,7 +43014,7 @@
         <v>45622</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>45671</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43160,7 +43160,7 @@
         <v>44980</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43238,7 +43238,7 @@
         <v>45581</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>45548</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>44516</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         <v>45033</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>45048</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43603,7 +43603,7 @@
         <v>44936</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43676,7 +43676,7 @@
         <v>45432</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>44811</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43822,7 +43822,7 @@
         <v>44707</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43895,7 +43895,7 @@
         <v>44501</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>45747</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44046,7 +44046,7 @@
         <v>45762</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44124,7 +44124,7 @@
         <v>46092</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44197,7 +44197,7 @@
         <v>46147</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44270,7 +44270,7 @@
         <v>46149</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>46155</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>

--- a/Översikt ROBERTSFORS.xlsx
+++ b/Översikt ROBERTSFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46097</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>45701</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>44919</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45250</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>45944</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>45936</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>45792</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>45939</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>46070</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>46135</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>45796</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>45967</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>45153</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>46050</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>45891</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45915</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>44725</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>45848</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>46037</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>45119</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>44535</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>45560</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>45937</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>46038</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>46050</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>46050</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>46050</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>45468</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>46307</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>46265</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>45051</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>45182</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>45504</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>45177</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>45182</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>44699</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>44559</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>44803</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>44497</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>45210</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>45695</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>45957</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>45510</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>44823</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>45233</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>46198</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>46204</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>46050</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>46050</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>46050</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>45827</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>45835</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         <v>45844</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>45182</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>45856</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>46269</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>45146</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
         <v>45719</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>45245</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         <v>45163</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>45176</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>45124</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>45153</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>45630</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>45712</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7883,7 +7883,7 @@
         <v>45245</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>44312</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>45747</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>45919</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         <v>44784</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>44810</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>44677</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>44880</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>44734</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         <v>44734</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>44858</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>44645</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>44572</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>44497</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         <v>44721</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>44658</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>44612</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         <v>44612</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
         <v>44641</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>44775</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         <v>44575</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>44735</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>44795</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>44855</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>44612</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>44519</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>44571</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         <v>44532</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>44844</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>44612</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>44612</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>44851</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10382,7 +10382,7 @@
         <v>44729</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>44819</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>44662</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>44697</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>44812</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>44827</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>44841</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>44824</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
         <v>44580</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>44574</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>44641</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>44644</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>44817</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>44615</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>44627</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>44627</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>44789</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>45042</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>45715</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>45268</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>45889</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>45890</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         <v>45890</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
         <v>45893</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>45607</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12237,7 +12237,7 @@
         <v>45895</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>45896</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>44502</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>44580</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>45029</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>45541</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>46160</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>45540</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>45909</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>45502</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>45580</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>45915</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>45918</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>45919</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>45470</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>45029</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>45924</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>45926</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         <v>45580</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13664,7 +13664,7 @@
         <v>44734</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>45386</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>46171</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>45929</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13961,7 +13961,7 @@
         <v>46170</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>46171</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>45076</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>45129</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14253,7 +14253,7 @@
         <v>46176</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>45938</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>46175</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14472,7 +14472,7 @@
         <v>45160</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>45250</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>46177</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>45782</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>45253</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>45454</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>46113</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>44945</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>45526</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>45090</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>46181</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>45461</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>46183</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>44904</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>46185</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>46185</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>45957</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>45958</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>45957</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>45959</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>46185</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>45959</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>46188</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16176,7 +16176,7 @@
         <v>45960</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>45961</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16332,7 +16332,7 @@
         <v>45965</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>45966</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16483,7 +16483,7 @@
         <v>45965</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16556,7 +16556,7 @@
         <v>46188</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16629,7 +16629,7 @@
         <v>46188</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>45965</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16775,7 +16775,7 @@
         <v>45965</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         <v>45530</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>45620</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16994,7 +16994,7 @@
         <v>45307</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17067,7 +17067,7 @@
         <v>45197</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         <v>45664</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>45659</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>45974</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17369,7 +17369,7 @@
         <v>45251</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>45148</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17525,7 +17525,7 @@
         <v>46198</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17598,7 +17598,7 @@
         <v>46202</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17671,7 +17671,7 @@
         <v>45525</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17744,7 +17744,7 @@
         <v>46203</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17817,7 +17817,7 @@
         <v>45981</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>45981</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17968,7 +17968,7 @@
         <v>45981</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18046,7 +18046,7 @@
         <v>45162</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18119,7 +18119,7 @@
         <v>46204</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18197,7 +18197,7 @@
         <v>45365</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>46205</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>44902</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18416,7 +18416,7 @@
         <v>46205</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18489,7 +18489,7 @@
         <v>45365</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18562,7 +18562,7 @@
         <v>45610</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>44980</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18713,7 +18713,7 @@
         <v>46206</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18786,7 +18786,7 @@
         <v>45987</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>45215</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18932,7 +18932,7 @@
         <v>45687</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>45545</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>44860</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>45551</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19224,7 +19224,7 @@
         <v>45635</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19297,7 +19297,7 @@
         <v>45628</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>45251</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19443,7 +19443,7 @@
         <v>45996</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19516,7 +19516,7 @@
         <v>46000</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>45458</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>45644</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>45628</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>45160</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19886,7 +19886,7 @@
         <v>46195</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>46000</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>45161</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>45246</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>46225</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20251,7 +20251,7 @@
         <v>45246</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20324,7 +20324,7 @@
         <v>46225</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
         <v>46225</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20470,7 +20470,7 @@
         <v>46230</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20543,7 +20543,7 @@
         <v>46279</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20616,7 +20616,7 @@
         <v>46279</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20694,7 +20694,7 @@
         <v>46280</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>46280</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>46279</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20928,7 +20928,7 @@
         <v>46279</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         <v>46239</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         <v>45642</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21152,7 +21152,7 @@
         <v>46282</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21225,7 +21225,7 @@
         <v>46240</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>46282</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>46239</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21449,7 +21449,7 @@
         <v>45495</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>46240</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>45544</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>46240</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>46240</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21824,7 +21824,7 @@
         <v>46239</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21897,7 +21897,7 @@
         <v>46283</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>46240</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>46185</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>45188</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22194,7 +22194,7 @@
         <v>46240</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>46240</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>44973</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22418,7 +22418,7 @@
         <v>46286</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22496,7 +22496,7 @@
         <v>46286</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>46037</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22647,7 +22647,7 @@
         <v>45794</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>46042</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22793,7 +22793,7 @@
         <v>46288</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22866,7 +22866,7 @@
         <v>46244</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>46048</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23012,7 +23012,7 @@
         <v>45761</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>45800</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>46288</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23236,7 +23236,7 @@
         <v>46050</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23309,7 +23309,7 @@
         <v>45800</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23382,7 +23382,7 @@
         <v>46188</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23455,7 +23455,7 @@
         <v>46050</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>46050</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
         <v>46191</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>46196</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23752,7 +23752,7 @@
         <v>45803</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>45803</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>46289</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23976,7 +23976,7 @@
         <v>46240</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
         <v>46289</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>46132</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24205,7 +24205,7 @@
         <v>45687</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         <v>46289</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24356,7 +24356,7 @@
         <v>46058</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24434,7 +24434,7 @@
         <v>46059</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>46059</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24580,7 +24580,7 @@
         <v>45636</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>46291</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
         <v>46063</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>45813</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>46065</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>45818</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>46065</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>46291</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25174,7 +25174,7 @@
         <v>45678</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>46076</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>46083</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25398,7 +25398,7 @@
         <v>45832</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25476,7 +25476,7 @@
         <v>45831</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25549,7 +25549,7 @@
         <v>45474</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25627,7 +25627,7 @@
         <v>45839</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>45839</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>45839</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25846,7 +25846,7 @@
         <v>45839</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>46297</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25997,7 +25997,7 @@
         <v>45839</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26070,7 +26070,7 @@
         <v>45839</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26143,7 +26143,7 @@
         <v>46254</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26216,7 +26216,7 @@
         <v>46297</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>45568</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26367,7 +26367,7 @@
         <v>46094</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>45841</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26518,7 +26518,7 @@
         <v>46297</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26596,7 +26596,7 @@
         <v>45841</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>46099</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26742,7 +26742,7 @@
         <v>46099</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>45496</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>46297</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26971,7 +26971,7 @@
         <v>46255</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>46255</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27117,7 +27117,7 @@
         <v>46104</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>46259</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>46112</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>46302</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27409,7 +27409,7 @@
         <v>46105</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27482,7 +27482,7 @@
         <v>46258</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         <v>45856</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         <v>45856</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>45856</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27774,7 +27774,7 @@
         <v>46258</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>45789</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27920,7 +27920,7 @@
         <v>46261</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>45870</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28071,7 +28071,7 @@
         <v>46261</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>46122</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28222,7 +28222,7 @@
         <v>46303</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28300,7 +28300,7 @@
         <v>46303</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28373,7 +28373,7 @@
         <v>46126</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28446,7 +28446,7 @@
         <v>45873</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28519,7 +28519,7 @@
         <v>46126</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28592,7 +28592,7 @@
         <v>46126</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>45631</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28738,7 +28738,7 @@
         <v>46132</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28816,7 +28816,7 @@
         <v>46262</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28894,7 +28894,7 @@
         <v>44913</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>45162</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>44876</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29113,7 +29113,7 @@
         <v>46239</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>46135</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29259,7 +29259,7 @@
         <v>45160</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29332,7 +29332,7 @@
         <v>46135</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29405,7 +29405,7 @@
         <v>46308</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29478,7 +29478,7 @@
         <v>46135</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29551,7 +29551,7 @@
         <v>44894</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29624,7 +29624,7 @@
         <v>44901</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29697,7 +29697,7 @@
         <v>45357</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29770,7 +29770,7 @@
         <v>46135</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29843,7 +29843,7 @@
         <v>46308</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29916,7 +29916,7 @@
         <v>46266</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>46266</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30062,7 +30062,7 @@
         <v>45901</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30140,7 +30140,7 @@
         <v>45617</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30213,7 +30213,7 @@
         <v>45734</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30286,7 +30286,7 @@
         <v>46268</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>46269</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30442,7 +30442,7 @@
         <v>45246</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30515,7 +30515,7 @@
         <v>46269</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30593,7 +30593,7 @@
         <v>46314</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30666,7 +30666,7 @@
         <v>46314</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30739,7 +30739,7 @@
         <v>45502</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30812,7 +30812,7 @@
         <v>46139</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         <v>46314</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30963,7 +30963,7 @@
         <v>45561</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31036,7 +31036,7 @@
         <v>46314</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31114,7 +31114,7 @@
         <v>45238</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31187,7 +31187,7 @@
         <v>46268</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>46269</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31338,7 +31338,7 @@
         <v>46269</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31416,7 +31416,7 @@
         <v>46314</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>46314</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31572,7 +31572,7 @@
         <v>46269</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31650,7 +31650,7 @@
         <v>46140</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>45145</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31806,7 +31806,7 @@
         <v>45030</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31879,7 +31879,7 @@
         <v>45929</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31957,7 +31957,7 @@
         <v>45636</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>46273</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>45826</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32176,7 +32176,7 @@
         <v>46315</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>46273</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32322,7 +32322,7 @@
         <v>46315</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32400,7 +32400,7 @@
         <v>46315</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32478,7 +32478,7 @@
         <v>45146</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32556,7 +32556,7 @@
         <v>45496</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32634,7 +32634,7 @@
         <v>45930</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>45404</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32780,7 +32780,7 @@
         <v>46276</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>46276</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32931,7 +32931,7 @@
         <v>46317</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33004,7 +33004,7 @@
         <v>46317</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33082,7 +33082,7 @@
         <v>45627</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33155,7 +33155,7 @@
         <v>45679</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33228,7 +33228,7 @@
         <v>46146</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33306,7 +33306,7 @@
         <v>45548</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33379,7 +33379,7 @@
         <v>46146</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>46148</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33525,7 +33525,7 @@
         <v>44732</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>46150</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33676,7 +33676,7 @@
         <v>45600</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>46153</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33822,7 +33822,7 @@
         <v>46153</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33900,7 +33900,7 @@
         <v>45184</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33978,7 +33978,7 @@
         <v>45246</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34051,7 +34051,7 @@
         <v>46153</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34124,7 +34124,7 @@
         <v>45559</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34202,7 +34202,7 @@
         <v>46153</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34280,7 +34280,7 @@
         <v>46155</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34353,7 +34353,7 @@
         <v>45712</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34426,7 +34426,7 @@
         <v>45251</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34504,7 +34504,7 @@
         <v>45559</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>45607</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34650,7 +34650,7 @@
         <v>46160</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34728,7 +34728,7 @@
         <v>45671</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34801,7 +34801,7 @@
         <v>46160</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34874,7 +34874,7 @@
         <v>44960</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34947,7 +34947,7 @@
         <v>44960</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35020,7 +35020,7 @@
         <v>44960</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35093,7 +35093,7 @@
         <v>45079</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35166,7 +35166,7 @@
         <v>45565</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35239,7 +35239,7 @@
         <v>45020</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35317,7 +35317,7 @@
         <v>44952</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35390,7 +35390,7 @@
         <v>44516</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35463,7 +35463,7 @@
         <v>45090</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35536,7 +35536,7 @@
         <v>45205</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>45715</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35687,7 +35687,7 @@
         <v>45659</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35760,7 +35760,7 @@
         <v>45667</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35838,7 +35838,7 @@
         <v>45661</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35911,7 +35911,7 @@
         <v>45664</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35984,7 +35984,7 @@
         <v>45184</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36057,7 +36057,7 @@
         <v>45635</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36130,7 +36130,7 @@
         <v>45033</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36203,7 +36203,7 @@
         <v>45644</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36276,7 +36276,7 @@
         <v>45458</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>45205</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36422,7 +36422,7 @@
         <v>45692</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36495,7 +36495,7 @@
         <v>45182</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36568,7 +36568,7 @@
         <v>45197</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36646,7 +36646,7 @@
         <v>45701</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36719,7 +36719,7 @@
         <v>45040</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36792,7 +36792,7 @@
         <v>45176</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36865,7 +36865,7 @@
         <v>45687</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>45005</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37011,7 +37011,7 @@
         <v>45636</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37084,7 +37084,7 @@
         <v>45002</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>45537</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37235,7 +37235,7 @@
         <v>45133</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37313,7 +37313,7 @@
         <v>45070</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37386,7 +37386,7 @@
         <v>45090</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37459,7 +37459,7 @@
         <v>44901</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37532,7 +37532,7 @@
         <v>44895</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37605,7 +37605,7 @@
         <v>45695</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37678,7 +37678,7 @@
         <v>44980</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37751,7 +37751,7 @@
         <v>45135</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37829,7 +37829,7 @@
         <v>45617</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37902,7 +37902,7 @@
         <v>45617</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37980,7 +37980,7 @@
         <v>44953</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>44571</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38126,7 +38126,7 @@
         <v>45587</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38204,7 +38204,7 @@
         <v>45405</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38277,7 +38277,7 @@
         <v>44901</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38350,7 +38350,7 @@
         <v>45019</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38423,7 +38423,7 @@
         <v>45610</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38501,7 +38501,7 @@
         <v>45572</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38574,7 +38574,7 @@
         <v>45049</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>45020</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38725,7 +38725,7 @@
         <v>45480</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38798,7 +38798,7 @@
         <v>45141</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38876,7 +38876,7 @@
         <v>45281</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38949,7 +38949,7 @@
         <v>45468</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39022,7 +39022,7 @@
         <v>45475</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39095,7 +39095,7 @@
         <v>45610</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>45149</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39251,7 +39251,7 @@
         <v>45474</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>45246</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39402,7 +39402,7 @@
         <v>45458</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39475,7 +39475,7 @@
         <v>44551</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39548,7 +39548,7 @@
         <v>45484</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39621,7 +39621,7 @@
         <v>45041</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>45302</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39767,7 +39767,7 @@
         <v>45583</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39840,7 +39840,7 @@
         <v>45405</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39913,7 +39913,7 @@
         <v>45005</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39986,7 +39986,7 @@
         <v>45335</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40059,7 +40059,7 @@
         <v>45082</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40132,7 +40132,7 @@
         <v>45712</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40205,7 +40205,7 @@
         <v>45512</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>45678</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>45182</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>45553</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40502,7 +40502,7 @@
         <v>45701</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40575,7 +40575,7 @@
         <v>45191</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40648,7 +40648,7 @@
         <v>44580</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40721,7 +40721,7 @@
         <v>45610</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40799,7 +40799,7 @@
         <v>44683</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40877,7 +40877,7 @@
         <v>45625</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40950,7 +40950,7 @@
         <v>45601</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41028,7 +41028,7 @@
         <v>44805</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41101,7 +41101,7 @@
         <v>45687</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41174,7 +41174,7 @@
         <v>45708</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41247,7 +41247,7 @@
         <v>44588</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41320,7 +41320,7 @@
         <v>44622</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41398,7 +41398,7 @@
         <v>45653</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41471,7 +41471,7 @@
         <v>45664</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41544,7 +41544,7 @@
         <v>44699</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41617,7 +41617,7 @@
         <v>45659</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41690,7 +41690,7 @@
         <v>45611</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>45670</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41836,7 +41836,7 @@
         <v>44838</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41909,7 +41909,7 @@
         <v>45446</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41982,7 +41982,7 @@
         <v>45700</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>45202</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42128,7 +42128,7 @@
         <v>45708</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>45756</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>44783</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42347,7 +42347,7 @@
         <v>45463</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42420,7 +42420,7 @@
         <v>45301</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42493,7 +42493,7 @@
         <v>45013</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>45537</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42644,7 +42644,7 @@
         <v>44938</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42717,7 +42717,7 @@
         <v>45261</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42790,7 +42790,7 @@
         <v>45468</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42863,7 +42863,7 @@
         <v>45644</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42936,7 +42936,7 @@
         <v>45510</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43014,7 +43014,7 @@
         <v>45622</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43087,7 +43087,7 @@
         <v>45671</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43160,7 +43160,7 @@
         <v>44980</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43238,7 +43238,7 @@
         <v>45581</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>45548</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>44516</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         <v>45033</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>45048</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43603,7 +43603,7 @@
         <v>44936</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43676,7 +43676,7 @@
         <v>45432</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>44811</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43822,7 +43822,7 @@
         <v>44707</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43895,7 +43895,7 @@
         <v>44501</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>45747</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44046,7 +44046,7 @@
         <v>45762</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44124,7 +44124,7 @@
         <v>46092</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44197,7 +44197,7 @@
         <v>46147</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44270,7 +44270,7 @@
         <v>46149</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>46155</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
